--- a/proyeccion/Proyeccion_Pagos.xlsx
+++ b/proyeccion/Proyeccion_Pagos.xlsx
@@ -41736,26 +41736,26 @@
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>G.M. AGRUPACION DE COLABORACION.</t>
+          <t>FUNDACION FECUNDART</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
         <is>
-          <t>30717358909</t>
+          <t>30709242195</t>
         </is>
       </c>
       <c r="E805" s="2" t="inlineStr">
         <is>
-          <t>00001-00015250</t>
+          <t>00006-00000081</t>
         </is>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G805" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H805" s="2" t="inlineStr">
         <is>
@@ -41768,11 +41768,11 @@
         </is>
       </c>
       <c r="J805" s="3" t="n">
-        <v>1042650.99</v>
+        <v>27370</v>
       </c>
       <c r="K805" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="K806" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -41878,7 +41878,7 @@
       </c>
       <c r="K807" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="K808" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -41984,7 +41984,7 @@
       </c>
       <c r="K809" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42037,7 +42037,7 @@
       </c>
       <c r="K810" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42054,17 +42054,17 @@
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>ECCO S. A. U.</t>
+          <t>DELFINO IRINA MARIEL</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
         <is>
-          <t>30602764032</t>
+          <t>27235506276</t>
         </is>
       </c>
       <c r="E811" s="2" t="inlineStr">
         <is>
-          <t>00203-00160517</t>
+          <t>00002-00000760</t>
         </is>
       </c>
       <c r="F811" s="2" t="inlineStr">
@@ -42073,7 +42073,7 @@
         </is>
       </c>
       <c r="G811" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H811" s="2" t="inlineStr">
         <is>
@@ -42086,11 +42086,11 @@
         </is>
       </c>
       <c r="J811" s="3" t="n">
-        <v>4392027.4</v>
+        <v>204000</v>
       </c>
       <c r="K811" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42107,17 +42107,17 @@
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>ECCO S. A. U.</t>
+          <t>DIAGNOSTICO Y TRATAMIENTO EN SALUD AMBULATORIA DEL INTERIOR S.R.L.</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
         <is>
-          <t>30602764032</t>
+          <t>30714473723</t>
         </is>
       </c>
       <c r="E812" s="2" t="inlineStr">
         <is>
-          <t>00203-00160516</t>
+          <t>00002-00002609</t>
         </is>
       </c>
       <c r="F812" s="2" t="inlineStr">
@@ -42126,7 +42126,7 @@
         </is>
       </c>
       <c r="G812" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H812" s="2" t="inlineStr">
         <is>
@@ -42139,11 +42139,11 @@
         </is>
       </c>
       <c r="J812" s="3" t="n">
-        <v>3076639.9</v>
+        <v>39467</v>
       </c>
       <c r="K812" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42160,26 +42160,26 @@
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>GRUPO OPTICO SA</t>
+          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
         <is>
-          <t>30709290866</t>
+          <t>30716142015</t>
         </is>
       </c>
       <c r="E813" s="2" t="inlineStr">
         <is>
-          <t>00015-00005147</t>
+          <t>00003-00000048</t>
         </is>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G813" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H813" s="2" t="inlineStr">
         <is>
@@ -42192,11 +42192,11 @@
         </is>
       </c>
       <c r="J813" s="3" t="n">
-        <v>186000</v>
+        <v>51536</v>
       </c>
       <c r="K813" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42213,17 +42213,17 @@
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
+          <t>SALOMON MARIO RAMIRO</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
         <is>
-          <t>30709956880</t>
+          <t>20342435212</t>
         </is>
       </c>
       <c r="E814" s="2" t="inlineStr">
         <is>
-          <t>00004-00005073</t>
+          <t>00007-00000013</t>
         </is>
       </c>
       <c r="F814" s="2" t="inlineStr">
@@ -42245,11 +42245,11 @@
         </is>
       </c>
       <c r="J814" s="3" t="n">
-        <v>7800446.33</v>
+        <v>1771000</v>
       </c>
       <c r="K814" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42266,22 +42266,22 @@
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
+          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
         <is>
-          <t>30709956880</t>
+          <t>30708890223</t>
         </is>
       </c>
       <c r="E815" s="2" t="inlineStr">
         <is>
-          <t>00004-00005072</t>
+          <t>00010-00005532</t>
         </is>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G815" s="2" t="n">
@@ -42298,11 +42298,11 @@
         </is>
       </c>
       <c r="J815" s="3" t="n">
-        <v>2098721.11</v>
+        <v>761962</v>
       </c>
       <c r="K815" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42319,22 +42319,22 @@
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
+          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
         <is>
-          <t>30709956880</t>
+          <t>30708890223</t>
         </is>
       </c>
       <c r="E816" s="2" t="inlineStr">
         <is>
-          <t>00003-00053880</t>
+          <t>00010-00005534</t>
         </is>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G816" s="2" t="n">
@@ -42351,11 +42351,11 @@
         </is>
       </c>
       <c r="J816" s="3" t="n">
-        <v>2080692.61</v>
+        <v>89301</v>
       </c>
       <c r="K816" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42372,22 +42372,22 @@
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
+          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
         <is>
-          <t>30709956880</t>
+          <t>30708890223</t>
         </is>
       </c>
       <c r="E817" s="2" t="inlineStr">
         <is>
-          <t>00003-00053877</t>
+          <t>00010-00005533</t>
         </is>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G817" s="2" t="n">
@@ -42404,11 +42404,11 @@
         </is>
       </c>
       <c r="J817" s="3" t="n">
-        <v>1158847.62</v>
+        <v>60678</v>
       </c>
       <c r="K817" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42435,7 +42435,7 @@
       </c>
       <c r="E818" s="2" t="inlineStr">
         <is>
-          <t>00004-00005078</t>
+          <t>00004-00005073</t>
         </is>
       </c>
       <c r="F818" s="2" t="inlineStr">
@@ -42457,11 +42457,11 @@
         </is>
       </c>
       <c r="J818" s="3" t="n">
-        <v>519353.14</v>
+        <v>7800446.33</v>
       </c>
       <c r="K818" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42488,12 +42488,12 @@
       </c>
       <c r="E819" s="2" t="inlineStr">
         <is>
-          <t>00003-00053883</t>
+          <t>00003-00053877</t>
         </is>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G819" s="2" t="n">
@@ -42510,11 +42510,11 @@
         </is>
       </c>
       <c r="J819" s="3" t="n">
-        <v>27625.66</v>
+        <v>1158847.62</v>
       </c>
       <c r="K819" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42531,17 +42531,17 @@
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>RUFFIN ESTEBAN MAURICIO</t>
+          <t>RIOS DARIO EDUARDO</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>20264366896</t>
+          <t>20161589862</t>
         </is>
       </c>
       <c r="E820" s="2" t="inlineStr">
         <is>
-          <t>00002-00000229</t>
+          <t>00003-00000200</t>
         </is>
       </c>
       <c r="F820" s="2" t="inlineStr">
@@ -42563,11 +42563,11 @@
         </is>
       </c>
       <c r="J820" s="3" t="n">
-        <v>21864.78</v>
+        <v>780862.08</v>
       </c>
       <c r="K820" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42620,7 +42620,7 @@
       </c>
       <c r="K821" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42673,7 +42673,7 @@
       </c>
       <c r="K822" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
       </c>
       <c r="K823" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42779,7 +42779,7 @@
       </c>
       <c r="K824" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42832,7 +42832,7 @@
       </c>
       <c r="K825" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42885,7 +42885,7 @@
       </c>
       <c r="K826" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="K827" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -42955,17 +42955,17 @@
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>SOP S R L</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>30681218285</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E828" s="2" t="inlineStr">
         <is>
-          <t>00009-00011612</t>
+          <t>00024-00023177</t>
         </is>
       </c>
       <c r="F828" s="2" t="inlineStr">
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="G828" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H828" s="2" t="inlineStr">
         <is>
@@ -42987,11 +42987,11 @@
         </is>
       </c>
       <c r="J828" s="3" t="n">
-        <v>1640472</v>
+        <v>725065.77</v>
       </c>
       <c r="K828" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43018,7 +43018,7 @@
       </c>
       <c r="E829" s="2" t="inlineStr">
         <is>
-          <t>203-162147</t>
+          <t>00203-00160516</t>
         </is>
       </c>
       <c r="F829" s="2" t="inlineStr">
@@ -43040,11 +43040,11 @@
         </is>
       </c>
       <c r="J829" s="3" t="n">
-        <v>3996654.02</v>
+        <v>3076639.9</v>
       </c>
       <c r="K829" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43061,26 +43061,26 @@
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>GRUPO OPTICO SA</t>
+          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>30709290866</t>
+          <t>30716142015</t>
         </is>
       </c>
       <c r="E830" s="2" t="inlineStr">
         <is>
-          <t>15-5180</t>
+          <t>00003-00000050</t>
         </is>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G830" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H830" s="2" t="inlineStr">
         <is>
@@ -43093,11 +43093,11 @@
         </is>
       </c>
       <c r="J830" s="3" t="n">
-        <v>216720</v>
+        <v>368144</v>
       </c>
       <c r="K830" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43114,17 +43114,17 @@
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>SOP S R L</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>30681218285</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E831" s="2" t="inlineStr">
         <is>
-          <t>00009-00011649</t>
+          <t>00024-00023155</t>
         </is>
       </c>
       <c r="F831" s="2" t="inlineStr">
@@ -43133,7 +43133,7 @@
         </is>
       </c>
       <c r="G831" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H831" s="2" t="inlineStr">
         <is>
@@ -43146,11 +43146,11 @@
         </is>
       </c>
       <c r="J831" s="3" t="n">
-        <v>2150250</v>
+        <v>10391656.65</v>
       </c>
       <c r="K831" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43167,17 +43167,17 @@
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>SOP S R L</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>30681218285</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E832" s="2" t="inlineStr">
         <is>
-          <t>9-11649</t>
+          <t>00024-00023154</t>
         </is>
       </c>
       <c r="F832" s="2" t="inlineStr">
@@ -43186,7 +43186,7 @@
         </is>
       </c>
       <c r="G832" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H832" s="2" t="inlineStr">
         <is>
@@ -43199,11 +43199,11 @@
         </is>
       </c>
       <c r="J832" s="3" t="n">
-        <v>2150250</v>
+        <v>5230519.21</v>
       </c>
       <c r="K832" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43220,17 +43220,17 @@
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION MUTUAL DOCTOR ESTEBAN LAUREANO MARADONA SALUD (AMMA SALUD)</t>
+          <t>SOP S R L</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
         <is>
-          <t>33711300789</t>
+          <t>30681218285</t>
         </is>
       </c>
       <c r="E833" s="2" t="inlineStr">
         <is>
-          <t>00005-00000490</t>
+          <t>9-11649</t>
         </is>
       </c>
       <c r="F833" s="2" t="inlineStr">
@@ -43239,7 +43239,7 @@
         </is>
       </c>
       <c r="G833" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H833" s="2" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         </is>
       </c>
       <c r="J833" s="3" t="n">
-        <v>17302</v>
+        <v>2150250</v>
       </c>
       <c r="K833" s="2" t="inlineStr">
         <is>
@@ -43268,22 +43268,22 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>ASOCIACION MUTUAL DOCTOR ESTEBAN LAUREANO MARADONA SALUD (AMMA SALUD)</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>33711300789</t>
         </is>
       </c>
       <c r="E834" s="2" t="inlineStr">
         <is>
-          <t>00015-00006514</t>
+          <t>00005-00000490</t>
         </is>
       </c>
       <c r="F834" s="2" t="inlineStr">
@@ -43292,7 +43292,7 @@
         </is>
       </c>
       <c r="G834" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H834" s="2" t="inlineStr">
         <is>
@@ -43305,11 +43305,11 @@
         </is>
       </c>
       <c r="J834" s="3" t="n">
-        <v>1973505.76</v>
+        <v>17302</v>
       </c>
       <c r="K834" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43326,17 +43326,17 @@
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
         <is>
-          <t>30689767946</t>
+          <t>30709956880</t>
         </is>
       </c>
       <c r="E835" s="2" t="inlineStr">
         <is>
-          <t>00015-00001507</t>
+          <t>00004-00005072</t>
         </is>
       </c>
       <c r="F835" s="2" t="inlineStr">
@@ -43358,11 +43358,11 @@
         </is>
       </c>
       <c r="J835" s="3" t="n">
-        <v>1779717.61</v>
+        <v>2098721.11</v>
       </c>
       <c r="K835" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43379,17 +43379,17 @@
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>CIDI S.A</t>
+          <t>INSTITUTO PRIVADO DE NEONATOLOGIA Y PEDIATRIA S.A.</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
         <is>
-          <t>30715190253</t>
+          <t>30659560093</t>
         </is>
       </c>
       <c r="E836" s="2" t="inlineStr">
         <is>
-          <t>00001-00006677</t>
+          <t>00500-00044031</t>
         </is>
       </c>
       <c r="F836" s="2" t="inlineStr">
@@ -43411,11 +43411,11 @@
         </is>
       </c>
       <c r="J836" s="3" t="n">
-        <v>809831.97</v>
+        <v>1292379.75</v>
       </c>
       <c r="K836" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43432,17 +43432,17 @@
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>INSTITUTO PRIVADO DE NEONATOLOGIA Y PEDIATRIA S.A.</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
         <is>
-          <t>30689767946</t>
+          <t>30659560093</t>
         </is>
       </c>
       <c r="E837" s="2" t="inlineStr">
         <is>
-          <t>00015-00001505</t>
+          <t>00500-00044035</t>
         </is>
       </c>
       <c r="F837" s="2" t="inlineStr">
@@ -43464,11 +43464,11 @@
         </is>
       </c>
       <c r="J837" s="3" t="n">
-        <v>774958.7</v>
+        <v>1287167.43</v>
       </c>
       <c r="K837" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43495,12 +43495,12 @@
       </c>
       <c r="E838" s="2" t="inlineStr">
         <is>
-          <t>00001-00006648</t>
+          <t>00001-00006677</t>
         </is>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G838" s="2" t="n">
@@ -43517,11 +43517,11 @@
         </is>
       </c>
       <c r="J838" s="3" t="n">
-        <v>504057.76</v>
+        <v>809831.97</v>
       </c>
       <c r="K838" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43538,22 +43538,22 @@
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
         <is>
-          <t>30689767946</t>
+          <t>30709956880</t>
         </is>
       </c>
       <c r="E839" s="2" t="inlineStr">
         <is>
-          <t>00015-00001646</t>
+          <t>00004-00005078</t>
         </is>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G839" s="2" t="n">
@@ -43570,11 +43570,11 @@
         </is>
       </c>
       <c r="J839" s="3" t="n">
-        <v>453371.83</v>
+        <v>519353.14</v>
       </c>
       <c r="K839" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43601,12 +43601,12 @@
       </c>
       <c r="E840" s="2" t="inlineStr">
         <is>
-          <t>00001-00006676</t>
+          <t>00001-00006648</t>
         </is>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G840" s="2" t="n">
@@ -43623,11 +43623,11 @@
         </is>
       </c>
       <c r="J840" s="3" t="n">
-        <v>301664.56</v>
+        <v>504057.76</v>
       </c>
       <c r="K840" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43644,22 +43644,22 @@
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>CIDI S.A</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
         <is>
-          <t>30689767946</t>
+          <t>30715190253</t>
         </is>
       </c>
       <c r="E841" s="2" t="inlineStr">
         <is>
-          <t>00015-00001506</t>
+          <t>00001-00006676</t>
         </is>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G841" s="2" t="n">
@@ -43676,11 +43676,11 @@
         </is>
       </c>
       <c r="J841" s="3" t="n">
-        <v>163500.39</v>
+        <v>301664.56</v>
       </c>
       <c r="K841" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43697,17 +43697,17 @@
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>LOYEAU ARIEL MAXIMILANO</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
         <is>
-          <t>20282716101</t>
+          <t>30689767946</t>
         </is>
       </c>
       <c r="E842" s="2" t="inlineStr">
         <is>
-          <t>00003-00000338</t>
+          <t>00015-00001504</t>
         </is>
       </c>
       <c r="F842" s="2" t="inlineStr">
@@ -43729,11 +43729,11 @@
         </is>
       </c>
       <c r="J842" s="3" t="n">
-        <v>160000</v>
+        <v>77495.87</v>
       </c>
       <c r="K842" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43750,22 +43750,22 @@
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>L A C E SA</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
         <is>
-          <t>30689767946</t>
+          <t>30698488677</t>
         </is>
       </c>
       <c r="E843" s="2" t="inlineStr">
         <is>
-          <t>00015-00001504</t>
+          <t>00082-00002027</t>
         </is>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G843" s="2" t="n">
@@ -43782,11 +43782,11 @@
         </is>
       </c>
       <c r="J843" s="3" t="n">
-        <v>77495.87</v>
+        <v>70415.36</v>
       </c>
       <c r="K843" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43803,17 +43803,17 @@
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>L A C E SA</t>
+          <t>CIDI S.A</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
         <is>
-          <t>30698488677</t>
+          <t>30715190253</t>
         </is>
       </c>
       <c r="E844" s="2" t="inlineStr">
         <is>
-          <t>00082-00002027</t>
+          <t>00001-00006647</t>
         </is>
       </c>
       <c r="F844" s="2" t="inlineStr">
@@ -43835,11 +43835,11 @@
         </is>
       </c>
       <c r="J844" s="3" t="n">
-        <v>70415.36</v>
+        <v>62397.29</v>
       </c>
       <c r="K844" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43866,12 +43866,12 @@
       </c>
       <c r="E845" s="2" t="inlineStr">
         <is>
-          <t>00082-00002028</t>
+          <t>00082-00002029</t>
         </is>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G845" s="2" t="n">
@@ -43888,11 +43888,11 @@
         </is>
       </c>
       <c r="J845" s="3" t="n">
-        <v>69897.60000000001</v>
+        <v>62131.2</v>
       </c>
       <c r="K845" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -43909,22 +43909,22 @@
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>CIDI S.A</t>
+          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
         <is>
-          <t>30715190253</t>
+          <t>30546670623</t>
         </is>
       </c>
       <c r="E846" s="2" t="inlineStr">
         <is>
-          <t>00001-00006647</t>
+          <t>00104-00000580</t>
         </is>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G846" s="2" t="n">
@@ -43941,7 +43941,7 @@
         </is>
       </c>
       <c r="J846" s="3" t="n">
-        <v>62397.29</v>
+        <v>48000</v>
       </c>
       <c r="K846" s="2" t="inlineStr">
         <is>
@@ -43962,22 +43962,22 @@
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>L A C E SA</t>
+          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
         <is>
-          <t>30698488677</t>
+          <t>30546670623</t>
         </is>
       </c>
       <c r="E847" s="2" t="inlineStr">
         <is>
-          <t>00082-00002029</t>
+          <t>00104-00000581</t>
         </is>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G847" s="2" t="n">
@@ -43994,7 +43994,7 @@
         </is>
       </c>
       <c r="J847" s="3" t="n">
-        <v>62131.2</v>
+        <v>32000</v>
       </c>
       <c r="K847" s="2" t="inlineStr">
         <is>
@@ -44015,22 +44015,22 @@
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
+          <t>SANATORIO CRUZ AZUL SRL</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
         <is>
-          <t>30546670623</t>
+          <t>30669419658</t>
         </is>
       </c>
       <c r="E848" s="2" t="inlineStr">
         <is>
-          <t>00104-00000580</t>
+          <t>00006-00006097</t>
         </is>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G848" s="2" t="n">
@@ -44047,11 +44047,11 @@
         </is>
       </c>
       <c r="J848" s="3" t="n">
-        <v>48000</v>
+        <v>30640</v>
       </c>
       <c r="K848" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44068,22 +44068,22 @@
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
+          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
         <is>
-          <t>30546670623</t>
+          <t>30709956880</t>
         </is>
       </c>
       <c r="E849" s="2" t="inlineStr">
         <is>
-          <t>00104-00000581</t>
+          <t>00003-00053883</t>
         </is>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G849" s="2" t="n">
@@ -44100,11 +44100,11 @@
         </is>
       </c>
       <c r="J849" s="3" t="n">
-        <v>32000</v>
+        <v>27625.66</v>
       </c>
       <c r="K849" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44121,17 +44121,17 @@
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>FUNDACION CENTRO PREVENCION Y ATENCION CONTRA BULIMIA Y ANOREXIA Y OTRAS ENFERMEDADES SOCIALES</t>
+          <t>FESER MARIA LAURA</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
         <is>
-          <t>30714398454</t>
+          <t>23202343104</t>
         </is>
       </c>
       <c r="E850" s="2" t="inlineStr">
         <is>
-          <t>4-2563</t>
+          <t>00002-00000462</t>
         </is>
       </c>
       <c r="F850" s="2" t="inlineStr">
@@ -44153,11 +44153,11 @@
         </is>
       </c>
       <c r="J850" s="3" t="n">
-        <v>600000</v>
+        <v>60000</v>
       </c>
       <c r="K850" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
       </c>
       <c r="K851" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44227,22 +44227,22 @@
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>RUFFIN ESTEBAN MAURICIO</t>
+          <t>ROENTGEN S A</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
         <is>
-          <t>20264366896</t>
+          <t>30642081183</t>
         </is>
       </c>
       <c r="E852" s="2" t="inlineStr">
         <is>
-          <t>00002-00000231</t>
+          <t>00017-00014155</t>
         </is>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G852" s="2" t="n">
@@ -44259,11 +44259,11 @@
         </is>
       </c>
       <c r="J852" s="3" t="n">
-        <v>909000</v>
+        <v>508186.56</v>
       </c>
       <c r="K852" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44280,26 +44280,26 @@
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>DELFINO IRINA MARIEL</t>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
         <is>
-          <t>27235506276</t>
+          <t>30623442566</t>
         </is>
       </c>
       <c r="E853" s="2" t="inlineStr">
         <is>
-          <t>00002-00000760</t>
+          <t>00004-00015610</t>
         </is>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G853" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H853" s="2" t="inlineStr">
         <is>
@@ -44312,11 +44312,11 @@
         </is>
       </c>
       <c r="J853" s="3" t="n">
-        <v>204000</v>
+        <v>38125.92</v>
       </c>
       <c r="K853" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44333,17 +44333,17 @@
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>PROYECTOS INNOVADORES S R L</t>
+          <t>SOP S R L</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
         <is>
-          <t>30709702978</t>
+          <t>30681218285</t>
         </is>
       </c>
       <c r="E854" s="2" t="inlineStr">
         <is>
-          <t>00002-00000100</t>
+          <t>00009-00011649</t>
         </is>
       </c>
       <c r="F854" s="2" t="inlineStr">
@@ -44352,7 +44352,7 @@
         </is>
       </c>
       <c r="G854" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H854" s="2" t="inlineStr">
         <is>
@@ -44365,11 +44365,11 @@
         </is>
       </c>
       <c r="J854" s="3" t="n">
-        <v>3630000</v>
+        <v>2150250</v>
       </c>
       <c r="K854" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44386,17 +44386,17 @@
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>SALOMON MARIO RAMIRO</t>
+          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
         <is>
-          <t>20342435212</t>
+          <t>30580553040</t>
         </is>
       </c>
       <c r="E855" s="2" t="inlineStr">
         <is>
-          <t>00007-00000013</t>
+          <t>00110-00022000</t>
         </is>
       </c>
       <c r="F855" s="2" t="inlineStr">
@@ -44418,11 +44418,11 @@
         </is>
       </c>
       <c r="J855" s="3" t="n">
-        <v>1771000</v>
+        <v>2021280.98</v>
       </c>
       <c r="K855" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44439,17 +44439,17 @@
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>MARIN DANIEL ALBERTO</t>
+          <t>RESONANCIA MAGNETICA SRL</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
         <is>
-          <t>20170008007</t>
+          <t>30694300487</t>
         </is>
       </c>
       <c r="E856" s="2" t="inlineStr">
         <is>
-          <t>00005-00000199</t>
+          <t>00005-00006007</t>
         </is>
       </c>
       <c r="F856" s="2" t="inlineStr">
@@ -44458,7 +44458,7 @@
         </is>
       </c>
       <c r="G856" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H856" s="2" t="inlineStr">
         <is>
@@ -44471,11 +44471,11 @@
         </is>
       </c>
       <c r="J856" s="3" t="n">
-        <v>858000</v>
+        <v>951358.6899999999</v>
       </c>
       <c r="K856" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44528,7 +44528,7 @@
       </c>
       <c r="K857" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44545,17 +44545,17 @@
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>RIOS DARIO EDUARDO</t>
+          <t>ROGGERO NORMA BEATRIZ</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
         <is>
-          <t>20161589862</t>
+          <t>27179300988</t>
         </is>
       </c>
       <c r="E858" s="2" t="inlineStr">
         <is>
-          <t>00003-00000200</t>
+          <t>00002-00000022</t>
         </is>
       </c>
       <c r="F858" s="2" t="inlineStr">
@@ -44577,11 +44577,11 @@
         </is>
       </c>
       <c r="J858" s="3" t="n">
-        <v>780862.08</v>
+        <v>419639.94</v>
       </c>
       <c r="K858" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44598,17 +44598,17 @@
       </c>
       <c r="C859" s="2" t="inlineStr">
         <is>
-          <t>ROGGERO NORMA BEATRIZ</t>
+          <t>VILLALBA MARIA EUGENIA</t>
         </is>
       </c>
       <c r="D859" s="2" t="inlineStr">
         <is>
-          <t>27179300988</t>
+          <t>23261030314</t>
         </is>
       </c>
       <c r="E859" s="2" t="inlineStr">
         <is>
-          <t>00002-00000022</t>
+          <t>00002-00000115</t>
         </is>
       </c>
       <c r="F859" s="2" t="inlineStr">
@@ -44630,7 +44630,7 @@
         </is>
       </c>
       <c r="J859" s="3" t="n">
-        <v>419639.94</v>
+        <v>244000</v>
       </c>
       <c r="K859" s="2" t="inlineStr">
         <is>
@@ -44651,17 +44651,17 @@
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>VILLALBA MARIA EUGENIA</t>
+          <t>BUGIA MARCELO LUIS</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
         <is>
-          <t>23261030314</t>
+          <t>20182544907</t>
         </is>
       </c>
       <c r="E860" s="2" t="inlineStr">
         <is>
-          <t>00002-00000115</t>
+          <t>00002-00000168</t>
         </is>
       </c>
       <c r="F860" s="2" t="inlineStr">
@@ -44683,11 +44683,11 @@
         </is>
       </c>
       <c r="J860" s="3" t="n">
-        <v>244000</v>
+        <v>189000</v>
       </c>
       <c r="K860" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44704,17 +44704,17 @@
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>BUGIA MARCELO LUIS</t>
+          <t>FUNDACION FECUNDART</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
         <is>
-          <t>20182544907</t>
+          <t>30709242195</t>
         </is>
       </c>
       <c r="E861" s="2" t="inlineStr">
         <is>
-          <t>00002-00000168</t>
+          <t>00006-00000082</t>
         </is>
       </c>
       <c r="F861" s="2" t="inlineStr">
@@ -44736,11 +44736,11 @@
         </is>
       </c>
       <c r="J861" s="3" t="n">
-        <v>189000</v>
+        <v>188789.6</v>
       </c>
       <c r="K861" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44793,7 +44793,7 @@
       </c>
       <c r="K862" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44810,17 +44810,17 @@
       </c>
       <c r="C863" s="2" t="inlineStr">
         <is>
-          <t>LOYEAU EDUARDO JORGE</t>
+          <t>LECOUSER S.A.</t>
         </is>
       </c>
       <c r="D863" s="2" t="inlineStr">
         <is>
-          <t>20101728820</t>
+          <t>33717029009</t>
         </is>
       </c>
       <c r="E863" s="2" t="inlineStr">
         <is>
-          <t>00002-00000179</t>
+          <t>00001-00001004</t>
         </is>
       </c>
       <c r="F863" s="2" t="inlineStr">
@@ -44829,7 +44829,7 @@
         </is>
       </c>
       <c r="G863" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H863" s="2" t="inlineStr">
         <is>
@@ -44842,11 +44842,11 @@
         </is>
       </c>
       <c r="J863" s="3" t="n">
-        <v>120000</v>
+        <v>165000</v>
       </c>
       <c r="K863" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44863,22 +44863,22 @@
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>GARRONE JESICA VALERIA</t>
+          <t>LOYEAU ARIEL MAXIMILANO</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
         <is>
-          <t>27256682104</t>
+          <t>20282716101</t>
         </is>
       </c>
       <c r="E864" s="2" t="inlineStr">
         <is>
-          <t>01001-00000128</t>
+          <t>00003-00000338</t>
         </is>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G864" s="2" t="n">
@@ -44895,11 +44895,11 @@
         </is>
       </c>
       <c r="J864" s="3" t="n">
-        <v>21000</v>
+        <v>160000</v>
       </c>
       <c r="K864" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44916,26 +44916,26 @@
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>AGUIRRE CARLOS ALBERTO</t>
+          <t>RESONANCIA MAGNETICA SRL</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
         <is>
-          <t>20079823997</t>
+          <t>30694300487</t>
         </is>
       </c>
       <c r="E865" s="2" t="inlineStr">
         <is>
-          <t>00002-00000261</t>
+          <t>00005-00006006</t>
         </is>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G865" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H865" s="2" t="inlineStr">
         <is>
@@ -44948,11 +44948,11 @@
         </is>
       </c>
       <c r="J865" s="3" t="n">
-        <v>15000</v>
+        <v>83094.35000000001</v>
       </c>
       <c r="K865" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -44979,12 +44979,12 @@
       </c>
       <c r="E866" s="2" t="inlineStr">
         <is>
-          <t>00002-00000262</t>
+          <t>00002-00000261</t>
         </is>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G866" s="2" t="n">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="K866" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45017,27 +45017,27 @@
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C867" s="2" t="inlineStr">
         <is>
-          <t>MIRANDA VERONICA ANABEL</t>
+          <t>AGUIRRE CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="D867" s="2" t="inlineStr">
         <is>
-          <t>27220344814</t>
+          <t>20079823997</t>
         </is>
       </c>
       <c r="E867" s="2" t="inlineStr">
         <is>
-          <t>00002-00000259</t>
+          <t>00002-00000262</t>
         </is>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G867" s="2" t="n">
@@ -45054,11 +45054,11 @@
         </is>
       </c>
       <c r="J867" s="3" t="n">
-        <v>1067000</v>
+        <v>15000</v>
       </c>
       <c r="K867" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45075,22 +45075,22 @@
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
+          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr">
         <is>
-          <t>30574596951</t>
+          <t>30709956880</t>
         </is>
       </c>
       <c r="E868" s="2" t="inlineStr">
         <is>
-          <t>00037-00027932</t>
+          <t>00003-00053880</t>
         </is>
       </c>
       <c r="F868" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G868" s="2" t="n">
@@ -45107,11 +45107,11 @@
         </is>
       </c>
       <c r="J868" s="3" t="n">
-        <v>791865.12</v>
+        <v>2080692.61</v>
       </c>
       <c r="K868" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45128,22 +45128,22 @@
       </c>
       <c r="C869" s="2" t="inlineStr">
         <is>
-          <t>CARNERO JORGE ALBERTO DEL VALLE</t>
+          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
         </is>
       </c>
       <c r="D869" s="2" t="inlineStr">
         <is>
-          <t>23264829119</t>
+          <t>30574596951</t>
         </is>
       </c>
       <c r="E869" s="2" t="inlineStr">
         <is>
-          <t>00002-00000186</t>
+          <t>00037-00027932</t>
         </is>
       </c>
       <c r="F869" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G869" s="2" t="n">
@@ -45160,11 +45160,11 @@
         </is>
       </c>
       <c r="J869" s="3" t="n">
-        <v>576000</v>
+        <v>791865.12</v>
       </c>
       <c r="K869" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45181,22 +45181,22 @@
       </c>
       <c r="C870" s="2" t="inlineStr">
         <is>
-          <t>CIRCULO DE PROFESIONALES DE LA REHABILITACION DEL DEPARTAMENTO SAN MARTIN</t>
+          <t>CARNERO JORGE ALBERTO DEL VALLE</t>
         </is>
       </c>
       <c r="D870" s="2" t="inlineStr">
         <is>
-          <t>30674856756</t>
+          <t>23264829119</t>
         </is>
       </c>
       <c r="E870" s="2" t="inlineStr">
         <is>
-          <t>4-3255</t>
+          <t>00002-00000186</t>
         </is>
       </c>
       <c r="F870" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G870" s="2" t="n">
@@ -45213,11 +45213,11 @@
         </is>
       </c>
       <c r="J870" s="3" t="n">
-        <v>465000</v>
+        <v>576000</v>
       </c>
       <c r="K870" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45234,17 +45234,17 @@
       </c>
       <c r="C871" s="2" t="inlineStr">
         <is>
-          <t>COCCO NATALIA</t>
+          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
         </is>
       </c>
       <c r="D871" s="2" t="inlineStr">
         <is>
-          <t>27405059202</t>
+          <t>33711273129</t>
         </is>
       </c>
       <c r="E871" s="2" t="inlineStr">
         <is>
-          <t>00003-00000286</t>
+          <t>00004-00012965</t>
         </is>
       </c>
       <c r="F871" s="2" t="inlineStr">
@@ -45253,7 +45253,7 @@
         </is>
       </c>
       <c r="G871" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H871" s="2" t="inlineStr">
         <is>
@@ -45266,11 +45266,11 @@
         </is>
       </c>
       <c r="J871" s="3" t="n">
-        <v>423000</v>
+        <v>497747.32</v>
       </c>
       <c r="K871" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45287,17 +45287,17 @@
       </c>
       <c r="C872" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MEDICO DE OLIVA</t>
+          <t>CIRCULO DE PROFESIONALES DE LA REHABILITACION DEL DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="D872" s="2" t="inlineStr">
         <is>
-          <t>30552575292</t>
+          <t>30674856756</t>
         </is>
       </c>
       <c r="E872" s="2" t="inlineStr">
         <is>
-          <t>00005-00002850</t>
+          <t>4-3255</t>
         </is>
       </c>
       <c r="F872" s="2" t="inlineStr">
@@ -45306,7 +45306,7 @@
         </is>
       </c>
       <c r="G872" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H872" s="2" t="inlineStr">
         <is>
@@ -45319,11 +45319,11 @@
         </is>
       </c>
       <c r="J872" s="3" t="n">
-        <v>413195.46</v>
+        <v>465000</v>
       </c>
       <c r="K872" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45340,22 +45340,22 @@
       </c>
       <c r="C873" s="2" t="inlineStr">
         <is>
-          <t>HEREDIA MARIA PAULA</t>
+          <t>COLEGIO MED REG DEL SUR DE CBA</t>
         </is>
       </c>
       <c r="D873" s="2" t="inlineStr">
         <is>
-          <t>23402492074</t>
+          <t>30553588266</t>
         </is>
       </c>
       <c r="E873" s="2" t="inlineStr">
         <is>
-          <t>00001-00000016</t>
+          <t>2-3583</t>
         </is>
       </c>
       <c r="F873" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G873" s="2" t="n">
@@ -45372,11 +45372,11 @@
         </is>
       </c>
       <c r="J873" s="3" t="n">
-        <v>319391.94</v>
+        <v>457115.8</v>
       </c>
       <c r="K873" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45393,17 +45393,17 @@
       </c>
       <c r="C874" s="2" t="inlineStr">
         <is>
-          <t>REBERTE MARICEL EDITH</t>
+          <t>COCCO NATALIA</t>
         </is>
       </c>
       <c r="D874" s="2" t="inlineStr">
         <is>
-          <t>27230899199</t>
+          <t>27405059202</t>
         </is>
       </c>
       <c r="E874" s="2" t="inlineStr">
         <is>
-          <t>00003-00000215</t>
+          <t>00003-00000286</t>
         </is>
       </c>
       <c r="F874" s="2" t="inlineStr">
@@ -45425,11 +45425,11 @@
         </is>
       </c>
       <c r="J874" s="3" t="n">
-        <v>216000</v>
+        <v>423000</v>
       </c>
       <c r="K874" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45446,17 +45446,17 @@
       </c>
       <c r="C875" s="2" t="inlineStr">
         <is>
-          <t>RESONANCIA MAGNETICA SRL</t>
+          <t>HEREDIA MARIA PAULA</t>
         </is>
       </c>
       <c r="D875" s="2" t="inlineStr">
         <is>
-          <t>30694300487</t>
+          <t>23402492074</t>
         </is>
       </c>
       <c r="E875" s="2" t="inlineStr">
         <is>
-          <t>00005-00005987</t>
+          <t>00001-00000016</t>
         </is>
       </c>
       <c r="F875" s="2" t="inlineStr">
@@ -45465,7 +45465,7 @@
         </is>
       </c>
       <c r="G875" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H875" s="2" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         </is>
       </c>
       <c r="J875" s="3" t="n">
-        <v>142623</v>
+        <v>319391.94</v>
       </c>
       <c r="K875" s="2" t="inlineStr">
         <is>
@@ -45499,26 +45499,26 @@
       </c>
       <c r="C876" s="2" t="inlineStr">
         <is>
-          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
+          <t>GRUPO OPTICO SA</t>
         </is>
       </c>
       <c r="D876" s="2" t="inlineStr">
         <is>
-          <t>30574596951</t>
+          <t>30709290866</t>
         </is>
       </c>
       <c r="E876" s="2" t="inlineStr">
         <is>
-          <t>00037-00027930</t>
+          <t>00015-00005147</t>
         </is>
       </c>
       <c r="F876" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G876" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H876" s="2" t="inlineStr">
         <is>
@@ -45531,11 +45531,11 @@
         </is>
       </c>
       <c r="J876" s="3" t="n">
-        <v>137160.74</v>
+        <v>186000</v>
       </c>
       <c r="K876" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45552,17 +45552,17 @@
       </c>
       <c r="C877" s="2" t="inlineStr">
         <is>
-          <t>CARDOSO FERNANDO MIGUEL</t>
+          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
         </is>
       </c>
       <c r="D877" s="2" t="inlineStr">
         <is>
-          <t>20288604208</t>
+          <t>30574596951</t>
         </is>
       </c>
       <c r="E877" s="2" t="inlineStr">
         <is>
-          <t>00006-00000114</t>
+          <t>00037-00027930</t>
         </is>
       </c>
       <c r="F877" s="2" t="inlineStr">
@@ -45584,11 +45584,11 @@
         </is>
       </c>
       <c r="J877" s="3" t="n">
-        <v>121500</v>
+        <v>137160.74</v>
       </c>
       <c r="K877" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45605,17 +45605,17 @@
       </c>
       <c r="C878" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MEDICO REGIONAL ARROYITO</t>
+          <t>CARDOSO FERNANDO MIGUEL</t>
         </is>
       </c>
       <c r="D878" s="2" t="inlineStr">
         <is>
-          <t>30555217419</t>
+          <t>20288604208</t>
         </is>
       </c>
       <c r="E878" s="2" t="inlineStr">
         <is>
-          <t>00004-00009702</t>
+          <t>00006-00000114</t>
         </is>
       </c>
       <c r="F878" s="2" t="inlineStr">
@@ -45637,11 +45637,11 @@
         </is>
       </c>
       <c r="J878" s="3" t="n">
-        <v>53488.34</v>
+        <v>121500</v>
       </c>
       <c r="K878" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45658,22 +45658,22 @@
       </c>
       <c r="C879" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO CRUZ AZUL SRL</t>
+          <t>LOYEAU EDUARDO JORGE</t>
         </is>
       </c>
       <c r="D879" s="2" t="inlineStr">
         <is>
-          <t>30669419658</t>
+          <t>20101728820</t>
         </is>
       </c>
       <c r="E879" s="2" t="inlineStr">
         <is>
-          <t>00006-00006097</t>
+          <t>00002-00000179</t>
         </is>
       </c>
       <c r="F879" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G879" s="2" t="n">
@@ -45690,11 +45690,11 @@
         </is>
       </c>
       <c r="J879" s="3" t="n">
-        <v>30640</v>
+        <v>120000</v>
       </c>
       <c r="K879" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45711,22 +45711,22 @@
       </c>
       <c r="C880" s="2" t="inlineStr">
         <is>
-          <t>COCCO NATALIA</t>
+          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
         </is>
       </c>
       <c r="D880" s="2" t="inlineStr">
         <is>
-          <t>27405059202</t>
+          <t>30580553040</t>
         </is>
       </c>
       <c r="E880" s="2" t="inlineStr">
         <is>
-          <t>00003-00000287</t>
+          <t>00110-00021995</t>
         </is>
       </c>
       <c r="F880" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G880" s="2" t="n">
@@ -45743,11 +45743,11 @@
         </is>
       </c>
       <c r="J880" s="3" t="n">
-        <v>17700.06</v>
+        <v>85884.33</v>
       </c>
       <c r="K880" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45764,26 +45764,26 @@
       </c>
       <c r="C881" s="2" t="inlineStr">
         <is>
-          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
+          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
         </is>
       </c>
       <c r="D881" s="2" t="inlineStr">
         <is>
-          <t>30574596951</t>
+          <t>33711273129</t>
         </is>
       </c>
       <c r="E881" s="2" t="inlineStr">
         <is>
-          <t>00037-00027931</t>
+          <t>00004-00012967</t>
         </is>
       </c>
       <c r="F881" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G881" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H881" s="2" t="inlineStr">
         <is>
@@ -45796,11 +45796,11 @@
         </is>
       </c>
       <c r="J881" s="3" t="n">
-        <v>3972.29</v>
+        <v>23262.96</v>
       </c>
       <c r="K881" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45812,27 +45812,27 @@
       </c>
       <c r="B882" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C882" s="2" t="inlineStr">
         <is>
-          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
+          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC ANON</t>
         </is>
       </c>
       <c r="D882" s="2" t="inlineStr">
         <is>
-          <t>30580553040</t>
+          <t>30574596951</t>
         </is>
       </c>
       <c r="E882" s="2" t="inlineStr">
         <is>
-          <t>00110-00022000</t>
+          <t>00037-00027931</t>
         </is>
       </c>
       <c r="F882" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G882" s="2" t="n">
@@ -45849,11 +45849,11 @@
         </is>
       </c>
       <c r="J882" s="3" t="n">
-        <v>2021280.98</v>
+        <v>3972.29</v>
       </c>
       <c r="K882" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45870,22 +45870,22 @@
       </c>
       <c r="C883" s="2" t="inlineStr">
         <is>
-          <t>ROENTGEN S A</t>
+          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDOBA</t>
         </is>
       </c>
       <c r="D883" s="2" t="inlineStr">
         <is>
-          <t>30642081183</t>
+          <t>33577427009</t>
         </is>
       </c>
       <c r="E883" s="2" t="inlineStr">
         <is>
-          <t>00017-00014155</t>
+          <t>00005-00005818</t>
         </is>
       </c>
       <c r="F883" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G883" s="2" t="n">
@@ -45902,11 +45902,11 @@
         </is>
       </c>
       <c r="J883" s="3" t="n">
-        <v>508186.56</v>
+        <v>1632036</v>
       </c>
       <c r="K883" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45923,17 +45923,17 @@
       </c>
       <c r="C884" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MED REG DEL SUR DE CBA</t>
+          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDOBA</t>
         </is>
       </c>
       <c r="D884" s="2" t="inlineStr">
         <is>
-          <t>30553588266</t>
+          <t>33577427009</t>
         </is>
       </c>
       <c r="E884" s="2" t="inlineStr">
         <is>
-          <t>2-3583</t>
+          <t>00005-00005817</t>
         </is>
       </c>
       <c r="F884" s="2" t="inlineStr">
@@ -45955,11 +45955,11 @@
         </is>
       </c>
       <c r="J884" s="3" t="n">
-        <v>457115.8</v>
+        <v>933853.5</v>
       </c>
       <c r="K884" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -45976,17 +45976,17 @@
       </c>
       <c r="C885" s="2" t="inlineStr">
         <is>
-          <t>RUCCI SILVANA LORENA</t>
+          <t>NIEVA MARIA EMILIA</t>
         </is>
       </c>
       <c r="D885" s="2" t="inlineStr">
         <is>
-          <t>27261075739</t>
+          <t>27361283843</t>
         </is>
       </c>
       <c r="E885" s="2" t="inlineStr">
         <is>
-          <t>00001-00000023</t>
+          <t>00002-00000222</t>
         </is>
       </c>
       <c r="F885" s="2" t="inlineStr">
@@ -46008,11 +46008,11 @@
         </is>
       </c>
       <c r="J885" s="3" t="n">
-        <v>440000</v>
+        <v>486457.8</v>
       </c>
       <c r="K885" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46029,17 +46029,17 @@
       </c>
       <c r="C886" s="2" t="inlineStr">
         <is>
-          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
+          <t>PEREIRA ALEJANDRO MANUEL</t>
         </is>
       </c>
       <c r="D886" s="2" t="inlineStr">
         <is>
-          <t>30580553040</t>
+          <t>20227934868</t>
         </is>
       </c>
       <c r="E886" s="2" t="inlineStr">
         <is>
-          <t>00110-00021997</t>
+          <t>00002-00000206</t>
         </is>
       </c>
       <c r="F886" s="2" t="inlineStr">
@@ -46061,11 +46061,11 @@
         </is>
       </c>
       <c r="J886" s="3" t="n">
-        <v>90667.33</v>
+        <v>475500</v>
       </c>
       <c r="K886" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46082,26 +46082,26 @@
       </c>
       <c r="C887" s="2" t="inlineStr">
         <is>
-          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
+          <t>RESONANCIA MAGNETICA SRL</t>
         </is>
       </c>
       <c r="D887" s="2" t="inlineStr">
         <is>
-          <t>30580553040</t>
+          <t>30694300487</t>
         </is>
       </c>
       <c r="E887" s="2" t="inlineStr">
         <is>
-          <t>00110-00021995</t>
+          <t>00005-00006011</t>
         </is>
       </c>
       <c r="F887" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G887" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H887" s="2" t="inlineStr">
         <is>
@@ -46114,11 +46114,11 @@
         </is>
       </c>
       <c r="J887" s="3" t="n">
-        <v>85884.33</v>
+        <v>244925.7</v>
       </c>
       <c r="K887" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46135,26 +46135,26 @@
       </c>
       <c r="C888" s="2" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ROENTGEN S.R.L.</t>
+          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S.A.</t>
         </is>
       </c>
       <c r="D888" s="2" t="inlineStr">
         <is>
-          <t>30715316338</t>
+          <t>30546133865</t>
         </is>
       </c>
       <c r="E888" s="2" t="inlineStr">
         <is>
-          <t>00003-00004640</t>
+          <t>00008-00012005</t>
         </is>
       </c>
       <c r="F888" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G888" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H888" s="2" t="inlineStr">
         <is>
@@ -46167,11 +46167,11 @@
         </is>
       </c>
       <c r="J888" s="3" t="n">
-        <v>70951.88</v>
+        <v>205601.57</v>
       </c>
       <c r="K888" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46188,22 +46188,22 @@
       </c>
       <c r="C889" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA REGIONAL S R L</t>
+          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
         </is>
       </c>
       <c r="D889" s="2" t="inlineStr">
         <is>
-          <t>30680944691</t>
+          <t>30580553040</t>
         </is>
       </c>
       <c r="E889" s="2" t="inlineStr">
         <is>
-          <t>00007-00002712</t>
+          <t>00110-00021997</t>
         </is>
       </c>
       <c r="F889" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G889" s="2" t="n">
@@ -46220,11 +46220,11 @@
         </is>
       </c>
       <c r="J889" s="3" t="n">
-        <v>60850</v>
+        <v>90667.33</v>
       </c>
       <c r="K889" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46241,26 +46241,26 @@
       </c>
       <c r="C890" s="2" t="inlineStr">
         <is>
-          <t>FESER MARIA LAURA</t>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
         </is>
       </c>
       <c r="D890" s="2" t="inlineStr">
         <is>
-          <t>23202343104</t>
+          <t>30623442566</t>
         </is>
       </c>
       <c r="E890" s="2" t="inlineStr">
         <is>
-          <t>00002-00000462</t>
+          <t>00004-00015611</t>
         </is>
       </c>
       <c r="F890" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G890" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H890" s="2" t="inlineStr">
         <is>
@@ -46273,11 +46273,11 @@
         </is>
       </c>
       <c r="J890" s="3" t="n">
-        <v>60000</v>
+        <v>87524.03999999999</v>
       </c>
       <c r="K890" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46294,22 +46294,22 @@
       </c>
       <c r="C891" s="2" t="inlineStr">
         <is>
-          <t>FESER MARIA LAURA</t>
+          <t>CENTRO MEDICO ROENTGEN S.R.L.</t>
         </is>
       </c>
       <c r="D891" s="2" t="inlineStr">
         <is>
-          <t>23202343104</t>
+          <t>30715316338</t>
         </is>
       </c>
       <c r="E891" s="2" t="inlineStr">
         <is>
-          <t>00002-00000463</t>
+          <t>00003-00004640</t>
         </is>
       </c>
       <c r="F891" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G891" s="2" t="n">
@@ -46326,11 +46326,11 @@
         </is>
       </c>
       <c r="J891" s="3" t="n">
-        <v>60000</v>
+        <v>70951.88</v>
       </c>
       <c r="K891" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46347,17 +46347,17 @@
       </c>
       <c r="C892" s="2" t="inlineStr">
         <is>
-          <t>DIAGNOSTICO Y TRATAMIENTO EN SALUD AMBULATORIA DEL INTERIOR S.R.L.</t>
+          <t>COCCO NATALIA</t>
         </is>
       </c>
       <c r="D892" s="2" t="inlineStr">
         <is>
-          <t>30714473723</t>
+          <t>27405059202</t>
         </is>
       </c>
       <c r="E892" s="2" t="inlineStr">
         <is>
-          <t>00002-00002609</t>
+          <t>00003-00000287</t>
         </is>
       </c>
       <c r="F892" s="2" t="inlineStr">
@@ -46379,11 +46379,11 @@
         </is>
       </c>
       <c r="J892" s="3" t="n">
-        <v>39467</v>
+        <v>17700.06</v>
       </c>
       <c r="K892" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46395,31 +46395,31 @@
       </c>
       <c r="B893" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C893" s="2" t="inlineStr">
         <is>
-          <t>CARRILLO ROMAN MARCEL</t>
+          <t>REYLES S.A.</t>
         </is>
       </c>
       <c r="D893" s="2" t="inlineStr">
         <is>
-          <t>20178729730</t>
+          <t>30708497629</t>
         </is>
       </c>
       <c r="E893" s="2" t="inlineStr">
         <is>
-          <t>00004-00000138</t>
+          <t>00010-00003784</t>
         </is>
       </c>
       <c r="F893" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G893" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H893" s="2" t="inlineStr">
         <is>
@@ -46432,11 +46432,11 @@
         </is>
       </c>
       <c r="J893" s="3" t="n">
-        <v>5712212.36</v>
+        <v>9705.6</v>
       </c>
       <c r="K893" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46453,22 +46453,22 @@
       </c>
       <c r="C894" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEL SOL S.A.</t>
+          <t>CARRILLO ROMAN MARCEL</t>
         </is>
       </c>
       <c r="D894" s="2" t="inlineStr">
         <is>
-          <t>30615571454</t>
+          <t>20178729730</t>
         </is>
       </c>
       <c r="E894" s="2" t="inlineStr">
         <is>
-          <t>8-20794</t>
+          <t>00004-00000138</t>
         </is>
       </c>
       <c r="F894" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G894" s="2" t="n">
@@ -46485,11 +46485,11 @@
         </is>
       </c>
       <c r="J894" s="3" t="n">
-        <v>2998785.71</v>
+        <v>5712212.36</v>
       </c>
       <c r="K894" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46506,17 +46506,17 @@
       </c>
       <c r="C895" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEL SOL S.A.</t>
+          <t>MIRANDA VERONICA ANABEL</t>
         </is>
       </c>
       <c r="D895" s="2" t="inlineStr">
         <is>
-          <t>30615571454</t>
+          <t>27220344814</t>
         </is>
       </c>
       <c r="E895" s="2" t="inlineStr">
         <is>
-          <t>8-20797</t>
+          <t>00002-00000259</t>
         </is>
       </c>
       <c r="F895" s="2" t="inlineStr">
@@ -46538,11 +46538,11 @@
         </is>
       </c>
       <c r="J895" s="3" t="n">
-        <v>2303237.09</v>
+        <v>1067000</v>
       </c>
       <c r="K895" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46559,17 +46559,17 @@
       </c>
       <c r="C896" s="2" t="inlineStr">
         <is>
-          <t>TOLEDO YOHANA ELIZABETH</t>
+          <t>CLINICA PRIVADA DEL SOL S.A.</t>
         </is>
       </c>
       <c r="D896" s="2" t="inlineStr">
         <is>
-          <t>27355742003</t>
+          <t>30615571454</t>
         </is>
       </c>
       <c r="E896" s="2" t="inlineStr">
         <is>
-          <t>00003-00000100</t>
+          <t>00008-00020901</t>
         </is>
       </c>
       <c r="F896" s="2" t="inlineStr">
@@ -46591,11 +46591,11 @@
         </is>
       </c>
       <c r="J896" s="3" t="n">
-        <v>558000</v>
+        <v>1053353.71</v>
       </c>
       <c r="K896" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46612,17 +46612,17 @@
       </c>
       <c r="C897" s="2" t="inlineStr">
         <is>
-          <t>PEREIRA ALEJANDRO MANUEL</t>
+          <t>MARIN DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="D897" s="2" t="inlineStr">
         <is>
-          <t>20227934868</t>
+          <t>20170008007</t>
         </is>
       </c>
       <c r="E897" s="2" t="inlineStr">
         <is>
-          <t>00002-00000206</t>
+          <t>00005-00000199</t>
         </is>
       </c>
       <c r="F897" s="2" t="inlineStr">
@@ -46644,11 +46644,11 @@
         </is>
       </c>
       <c r="J897" s="3" t="n">
-        <v>475500</v>
+        <v>858000</v>
       </c>
       <c r="K897" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46665,17 +46665,17 @@
       </c>
       <c r="C898" s="2" t="inlineStr">
         <is>
-          <t>SANCHEZ LUIS FERNANDO</t>
+          <t>TOLEDO YOHANA ELIZABETH</t>
         </is>
       </c>
       <c r="D898" s="2" t="inlineStr">
         <is>
-          <t>20927934281</t>
+          <t>27355742003</t>
         </is>
       </c>
       <c r="E898" s="2" t="inlineStr">
         <is>
-          <t>00002-00000163</t>
+          <t>00003-00000100</t>
         </is>
       </c>
       <c r="F898" s="2" t="inlineStr">
@@ -46697,7 +46697,7 @@
         </is>
       </c>
       <c r="J898" s="3" t="n">
-        <v>260000</v>
+        <v>558000</v>
       </c>
       <c r="K898" s="2" t="inlineStr">
         <is>
@@ -46718,26 +46718,26 @@
       </c>
       <c r="C899" s="2" t="inlineStr">
         <is>
-          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
+          <t>SOLBO S.A.S.</t>
         </is>
       </c>
       <c r="D899" s="2" t="inlineStr">
         <is>
-          <t>30566661663</t>
+          <t>30716784386</t>
         </is>
       </c>
       <c r="E899" s="2" t="inlineStr">
         <is>
-          <t>5-7127</t>
+          <t>1-465</t>
         </is>
       </c>
       <c r="F899" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G899" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H899" s="2" t="inlineStr">
         <is>
@@ -46750,11 +46750,11 @@
         </is>
       </c>
       <c r="J899" s="3" t="n">
-        <v>227084</v>
+        <v>334475.69</v>
       </c>
       <c r="K899" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46771,17 +46771,17 @@
       </c>
       <c r="C900" s="2" t="inlineStr">
         <is>
-          <t>MOLINA MARIA FERNANDA</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D900" s="2" t="inlineStr">
         <is>
-          <t>27307653406</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E900" s="2" t="inlineStr">
         <is>
-          <t>00003-00000293</t>
+          <t>00024-00023156</t>
         </is>
       </c>
       <c r="F900" s="2" t="inlineStr">
@@ -46790,7 +46790,7 @@
         </is>
       </c>
       <c r="G900" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H900" s="2" t="inlineStr">
         <is>
@@ -46803,11 +46803,11 @@
         </is>
       </c>
       <c r="J900" s="3" t="n">
-        <v>200000</v>
+        <v>324557.81</v>
       </c>
       <c r="K900" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46824,17 +46824,17 @@
       </c>
       <c r="C901" s="2" t="inlineStr">
         <is>
-          <t>TOLEDO YOHANA ELIZABETH</t>
+          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
         </is>
       </c>
       <c r="D901" s="2" t="inlineStr">
         <is>
-          <t>27355742003</t>
+          <t>30566661663</t>
         </is>
       </c>
       <c r="E901" s="2" t="inlineStr">
         <is>
-          <t>00003-00000101</t>
+          <t>5-7127</t>
         </is>
       </c>
       <c r="F901" s="2" t="inlineStr">
@@ -46856,11 +46856,11 @@
         </is>
       </c>
       <c r="J901" s="3" t="n">
-        <v>104359.2</v>
+        <v>227084</v>
       </c>
       <c r="K901" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46877,22 +46877,22 @@
       </c>
       <c r="C902" s="2" t="inlineStr">
         <is>
-          <t>MOLINA MARIA FERNANDA</t>
+          <t>CLINICA PRIVADA DEL SOL S.A.</t>
         </is>
       </c>
       <c r="D902" s="2" t="inlineStr">
         <is>
-          <t>27307653406</t>
+          <t>30615571454</t>
         </is>
       </c>
       <c r="E902" s="2" t="inlineStr">
         <is>
-          <t>00003-00000294</t>
+          <t>00008-00020902</t>
         </is>
       </c>
       <c r="F902" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G902" s="2" t="n">
@@ -46909,11 +46909,11 @@
         </is>
       </c>
       <c r="J902" s="3" t="n">
-        <v>25300</v>
+        <v>158885.19</v>
       </c>
       <c r="K902" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -46925,22 +46925,22 @@
       </c>
       <c r="B903" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C903" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION PRESTADORES DE HEMODIALISIS Y TRANSPLANTES RENALES DEL CENTRO (APHE Y TRC)</t>
+          <t>TOLEDO YOHANA ELIZABETH</t>
         </is>
       </c>
       <c r="D903" s="2" t="inlineStr">
         <is>
-          <t>30644610256</t>
+          <t>27355742003</t>
         </is>
       </c>
       <c r="E903" s="2" t="inlineStr">
         <is>
-          <t>3-8440</t>
+          <t>00003-00000101</t>
         </is>
       </c>
       <c r="F903" s="2" t="inlineStr">
@@ -46962,7 +46962,7 @@
         </is>
       </c>
       <c r="J903" s="3" t="n">
-        <v>22620000</v>
+        <v>104359.2</v>
       </c>
       <c r="K903" s="2" t="inlineStr">
         <is>
@@ -46978,27 +46978,27 @@
       </c>
       <c r="B904" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C904" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
+          <t>MOLINA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="D904" s="2" t="inlineStr">
         <is>
-          <t>30678724447</t>
+          <t>27307653406</t>
         </is>
       </c>
       <c r="E904" s="2" t="inlineStr">
         <is>
-          <t>00004-00019037</t>
+          <t>00003-00000294</t>
         </is>
       </c>
       <c r="F904" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G904" s="2" t="n">
@@ -47015,11 +47015,11 @@
         </is>
       </c>
       <c r="J904" s="3" t="n">
-        <v>5597532.12</v>
+        <v>25300</v>
       </c>
       <c r="K904" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47046,12 +47046,12 @@
       </c>
       <c r="E905" s="2" t="inlineStr">
         <is>
-          <t>3-8439</t>
+          <t>3-8440</t>
         </is>
       </c>
       <c r="F905" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G905" s="2" t="n">
@@ -47068,11 +47068,11 @@
         </is>
       </c>
       <c r="J905" s="3" t="n">
-        <v>3380000</v>
+        <v>22620000</v>
       </c>
       <c r="K905" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47099,7 +47099,7 @@
       </c>
       <c r="E906" s="2" t="inlineStr">
         <is>
-          <t>00004-00019018</t>
+          <t>00004-00019037</t>
         </is>
       </c>
       <c r="F906" s="2" t="inlineStr">
@@ -47121,11 +47121,11 @@
         </is>
       </c>
       <c r="J906" s="3" t="n">
-        <v>3064683</v>
+        <v>5597532.12</v>
       </c>
       <c r="K906" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47142,22 +47142,22 @@
       </c>
       <c r="C907" s="2" t="inlineStr">
         <is>
-          <t>ARNODO DANIEL</t>
+          <t>ASOCIACION PRESTADORES DE HEMODIALISIS Y TRANSPLANTES RENALES DEL CENTRO (APHE Y TRC)</t>
         </is>
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t>20282488796</t>
+          <t>30644610256</t>
         </is>
       </c>
       <c r="E907" s="2" t="inlineStr">
         <is>
-          <t>00003-00000233</t>
+          <t>3-8439</t>
         </is>
       </c>
       <c r="F907" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G907" s="2" t="n">
@@ -47174,11 +47174,11 @@
         </is>
       </c>
       <c r="J907" s="3" t="n">
-        <v>2038000</v>
+        <v>3380000</v>
       </c>
       <c r="K907" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47195,17 +47195,17 @@
       </c>
       <c r="C908" s="2" t="inlineStr">
         <is>
-          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDOBA</t>
+          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
         </is>
       </c>
       <c r="D908" s="2" t="inlineStr">
         <is>
-          <t>33577427009</t>
+          <t>30678724447</t>
         </is>
       </c>
       <c r="E908" s="2" t="inlineStr">
         <is>
-          <t>00005-00005818</t>
+          <t>00004-00019018</t>
         </is>
       </c>
       <c r="F908" s="2" t="inlineStr">
@@ -47227,11 +47227,11 @@
         </is>
       </c>
       <c r="J908" s="3" t="n">
-        <v>1632036</v>
+        <v>3064683</v>
       </c>
       <c r="K908" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47248,22 +47248,22 @@
       </c>
       <c r="C909" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
+          <t>ARNODO DANIEL</t>
         </is>
       </c>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t>30678724447</t>
+          <t>20282488796</t>
         </is>
       </c>
       <c r="E909" s="2" t="inlineStr">
         <is>
-          <t>00004-00019020</t>
+          <t>00003-00000233</t>
         </is>
       </c>
       <c r="F909" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G909" s="2" t="n">
@@ -47280,11 +47280,11 @@
         </is>
       </c>
       <c r="J909" s="3" t="n">
-        <v>957954</v>
+        <v>2038000</v>
       </c>
       <c r="K909" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47301,17 +47301,17 @@
       </c>
       <c r="C910" s="2" t="inlineStr">
         <is>
-          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDOBA</t>
+          <t>G.M. AGRUPACION DE COLABORACION.</t>
         </is>
       </c>
       <c r="D910" s="2" t="inlineStr">
         <is>
-          <t>33577427009</t>
+          <t>30717358909</t>
         </is>
       </c>
       <c r="E910" s="2" t="inlineStr">
         <is>
-          <t>00005-00005817</t>
+          <t>00001-00015250</t>
         </is>
       </c>
       <c r="F910" s="2" t="inlineStr">
@@ -47320,7 +47320,7 @@
         </is>
       </c>
       <c r="G910" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H910" s="2" t="inlineStr">
         <is>
@@ -47333,11 +47333,11 @@
         </is>
       </c>
       <c r="J910" s="3" t="n">
-        <v>933853.5</v>
+        <v>1042650.99</v>
       </c>
       <c r="K910" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47354,22 +47354,22 @@
       </c>
       <c r="C911" s="2" t="inlineStr">
         <is>
-          <t>NIEVA MARIA EMILIA</t>
+          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
         </is>
       </c>
       <c r="D911" s="2" t="inlineStr">
         <is>
-          <t>27361283843</t>
+          <t>30678724447</t>
         </is>
       </c>
       <c r="E911" s="2" t="inlineStr">
         <is>
-          <t>00002-00000222</t>
+          <t>00004-00019020</t>
         </is>
       </c>
       <c r="F911" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G911" s="2" t="n">
@@ -47386,11 +47386,11 @@
         </is>
       </c>
       <c r="J911" s="3" t="n">
-        <v>486457.8</v>
+        <v>957954</v>
       </c>
       <c r="K911" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47407,26 +47407,26 @@
       </c>
       <c r="C912" s="2" t="inlineStr">
         <is>
-          <t>GILETTA CLAUDIA VIVIANA</t>
+          <t>ESTIX S.A.S.</t>
         </is>
       </c>
       <c r="D912" s="2" t="inlineStr">
         <is>
-          <t>27208730768</t>
+          <t>30717147835</t>
         </is>
       </c>
       <c r="E912" s="2" t="inlineStr">
         <is>
-          <t>00002-00000047</t>
+          <t>4-471</t>
         </is>
       </c>
       <c r="F912" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G912" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H912" s="2" t="inlineStr">
         <is>
@@ -47439,11 +47439,11 @@
         </is>
       </c>
       <c r="J912" s="3" t="n">
-        <v>441000</v>
+        <v>528390.64</v>
       </c>
       <c r="K912" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47460,17 +47460,17 @@
       </c>
       <c r="C913" s="2" t="inlineStr">
         <is>
-          <t>EQUILIBRE SALUD S.A.S.</t>
+          <t>COLEGIO MEDICO DE OLIVA</t>
         </is>
       </c>
       <c r="D913" s="2" t="inlineStr">
         <is>
-          <t>33716532629</t>
+          <t>30552575292</t>
         </is>
       </c>
       <c r="E913" s="2" t="inlineStr">
         <is>
-          <t>1-636</t>
+          <t>00005-00002850</t>
         </is>
       </c>
       <c r="F913" s="2" t="inlineStr">
@@ -47479,7 +47479,7 @@
         </is>
       </c>
       <c r="G913" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H913" s="2" t="inlineStr">
         <is>
@@ -47492,11 +47492,11 @@
         </is>
       </c>
       <c r="J913" s="3" t="n">
-        <v>245598.2</v>
+        <v>413195.46</v>
       </c>
       <c r="K913" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47513,22 +47513,22 @@
       </c>
       <c r="C914" s="2" t="inlineStr">
         <is>
-          <t>ARNODO DANIEL</t>
+          <t>EQUILIBRE SALUD S.A.S.</t>
         </is>
       </c>
       <c r="D914" s="2" t="inlineStr">
         <is>
-          <t>20282488796</t>
+          <t>33716532629</t>
         </is>
       </c>
       <c r="E914" s="2" t="inlineStr">
         <is>
-          <t>00003-00000234</t>
+          <t>1-636</t>
         </is>
       </c>
       <c r="F914" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G914" s="2" t="n">
@@ -47545,11 +47545,11 @@
         </is>
       </c>
       <c r="J914" s="3" t="n">
-        <v>94488.45</v>
+        <v>245598.2</v>
       </c>
       <c r="K914" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47566,17 +47566,17 @@
       </c>
       <c r="C915" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PSICOLOGOS DE LA PROV. DE CORDOBA</t>
+          <t>MOLINA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="D915" s="2" t="inlineStr">
         <is>
-          <t>30680948891</t>
+          <t>27307653406</t>
         </is>
       </c>
       <c r="E915" s="2" t="inlineStr">
         <is>
-          <t>000012-0000851</t>
+          <t>00003-00000293</t>
         </is>
       </c>
       <c r="F915" s="2" t="inlineStr">
@@ -47598,11 +47598,11 @@
         </is>
       </c>
       <c r="J915" s="3" t="n">
-        <v>78624</v>
+        <v>200000</v>
       </c>
       <c r="K915" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47619,22 +47619,22 @@
       </c>
       <c r="C916" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
+          <t>ARNODO DANIEL</t>
         </is>
       </c>
       <c r="D916" s="2" t="inlineStr">
         <is>
-          <t>30678724447</t>
+          <t>20282488796</t>
         </is>
       </c>
       <c r="E916" s="2" t="inlineStr">
         <is>
-          <t>00004-00019019</t>
+          <t>00003-00000234</t>
         </is>
       </c>
       <c r="F916" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G916" s="2" t="n">
@@ -47651,11 +47651,11 @@
         </is>
       </c>
       <c r="J916" s="3" t="n">
-        <v>72074.63</v>
+        <v>94488.45</v>
       </c>
       <c r="K916" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47672,22 +47672,22 @@
       </c>
       <c r="C917" s="2" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MEDICOS PATOLOGOS Y CITOPATOLOGOS DE LA PCIA. DE CORDOBA</t>
+          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA DE CORDOBA A C L I N O R</t>
         </is>
       </c>
       <c r="D917" s="2" t="inlineStr">
         <is>
-          <t>30707403809</t>
+          <t>30678724447</t>
         </is>
       </c>
       <c r="E917" s="2" t="inlineStr">
         <is>
-          <t>00002-00003434</t>
+          <t>00004-00019019</t>
         </is>
       </c>
       <c r="F917" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G917" s="2" t="n">
@@ -47704,11 +47704,11 @@
         </is>
       </c>
       <c r="J917" s="3" t="n">
-        <v>25650</v>
+        <v>72074.63</v>
       </c>
       <c r="K917" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47735,12 +47735,12 @@
       </c>
       <c r="E918" s="2" t="inlineStr">
         <is>
-          <t>00002-00003433</t>
+          <t>00002-00003434</t>
         </is>
       </c>
       <c r="F918" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G918" s="2" t="n">
@@ -47757,11 +47757,11 @@
         </is>
       </c>
       <c r="J918" s="3" t="n">
-        <v>17700</v>
+        <v>25650</v>
       </c>
       <c r="K918" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47773,27 +47773,27 @@
       </c>
       <c r="B919" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C919" s="2" t="inlineStr">
         <is>
-          <t>EDUARDO JORGE LOYEAU</t>
+          <t>EQUILIBRE SALUD S.A.S.</t>
         </is>
       </c>
       <c r="D919" s="2" t="inlineStr">
         <is>
-          <t>20101728820</t>
+          <t>33716532629</t>
         </is>
       </c>
       <c r="E919" s="2" t="inlineStr">
         <is>
-          <t>2-178</t>
+          <t>00001-00000635</t>
         </is>
       </c>
       <c r="F919" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G919" s="2" t="n">
@@ -47810,11 +47810,11 @@
         </is>
       </c>
       <c r="J919" s="3" t="n">
-        <v>825000</v>
+        <v>17862</v>
       </c>
       <c r="K919" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47826,27 +47826,27 @@
       </c>
       <c r="B920" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C920" s="2" t="inlineStr">
         <is>
-          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
+          <t>ASOCIACION DE MEDICOS PATOLOGOS Y CITOPATOLOGOS DE LA PCIA. DE CORDOBA</t>
         </is>
       </c>
       <c r="D920" s="2" t="inlineStr">
         <is>
-          <t>30708890223</t>
+          <t>30707403809</t>
         </is>
       </c>
       <c r="E920" s="2" t="inlineStr">
         <is>
-          <t>00010-00005532</t>
+          <t>00002-00003433</t>
         </is>
       </c>
       <c r="F920" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G920" s="2" t="n">
@@ -47863,11 +47863,11 @@
         </is>
       </c>
       <c r="J920" s="3" t="n">
-        <v>761962</v>
+        <v>17700</v>
       </c>
       <c r="K920" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47884,17 +47884,17 @@
       </c>
       <c r="C921" s="2" t="inlineStr">
         <is>
-          <t>FUNDACION FECUNDART</t>
+          <t>ECCO S. A. U.</t>
         </is>
       </c>
       <c r="D921" s="2" t="inlineStr">
         <is>
-          <t>30709242195</t>
+          <t>30602764032</t>
         </is>
       </c>
       <c r="E921" s="2" t="inlineStr">
         <is>
-          <t>00006-00000082</t>
+          <t>00203-00160517</t>
         </is>
       </c>
       <c r="F921" s="2" t="inlineStr">
@@ -47903,7 +47903,7 @@
         </is>
       </c>
       <c r="G921" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H921" s="2" t="inlineStr">
         <is>
@@ -47916,11 +47916,11 @@
         </is>
       </c>
       <c r="J921" s="3" t="n">
-        <v>188789.6</v>
+        <v>4392027.4</v>
       </c>
       <c r="K921" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47937,22 +47937,22 @@
       </c>
       <c r="C922" s="2" t="inlineStr">
         <is>
-          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
+          <t>RUFFIN ESTEBAN MAURICIO</t>
         </is>
       </c>
       <c r="D922" s="2" t="inlineStr">
         <is>
-          <t>30708890223</t>
+          <t>20264366896</t>
         </is>
       </c>
       <c r="E922" s="2" t="inlineStr">
         <is>
-          <t>00010-00005534</t>
+          <t>00002-00000231</t>
         </is>
       </c>
       <c r="F922" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G922" s="2" t="n">
@@ -47969,11 +47969,11 @@
         </is>
       </c>
       <c r="J922" s="3" t="n">
-        <v>89301</v>
+        <v>909000</v>
       </c>
       <c r="K922" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -47990,17 +47990,17 @@
       </c>
       <c r="C923" s="2" t="inlineStr">
         <is>
-          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
+          <t>FUNDACION CENTRO PREVENCION Y ATENCION CONTRA BULIMIA Y ANOREXIA Y OTRAS ENFERMEDADES SOCIALES</t>
         </is>
       </c>
       <c r="D923" s="2" t="inlineStr">
         <is>
-          <t>30708890223</t>
+          <t>30714398454</t>
         </is>
       </c>
       <c r="E923" s="2" t="inlineStr">
         <is>
-          <t>00010-00005533</t>
+          <t>4-2563</t>
         </is>
       </c>
       <c r="F923" s="2" t="inlineStr">
@@ -48022,11 +48022,11 @@
         </is>
       </c>
       <c r="J923" s="3" t="n">
-        <v>60678</v>
+        <v>600000</v>
       </c>
       <c r="K923" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48043,17 +48043,17 @@
       </c>
       <c r="C924" s="2" t="inlineStr">
         <is>
-          <t>FUNDACION FECUNDART</t>
+          <t>RUCCI SILVANA LORENA</t>
         </is>
       </c>
       <c r="D924" s="2" t="inlineStr">
         <is>
-          <t>30709242195</t>
+          <t>27261075739</t>
         </is>
       </c>
       <c r="E924" s="2" t="inlineStr">
         <is>
-          <t>00006-00000081</t>
+          <t>00001-00000023</t>
         </is>
       </c>
       <c r="F924" s="2" t="inlineStr">
@@ -48075,11 +48075,11 @@
         </is>
       </c>
       <c r="J924" s="3" t="n">
-        <v>27370</v>
+        <v>440000</v>
       </c>
       <c r="K924" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48091,22 +48091,22 @@
       </c>
       <c r="B925" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C925" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEL SOL S.A.</t>
+          <t>FESER MARIA LAURA</t>
         </is>
       </c>
       <c r="D925" s="2" t="inlineStr">
         <is>
-          <t>30615571454</t>
+          <t>23202343104</t>
         </is>
       </c>
       <c r="E925" s="2" t="inlineStr">
         <is>
-          <t>00008-00020901</t>
+          <t>00002-00000463</t>
         </is>
       </c>
       <c r="F925" s="2" t="inlineStr">
@@ -48128,11 +48128,11 @@
         </is>
       </c>
       <c r="J925" s="3" t="n">
-        <v>1053353.71</v>
+        <v>60000</v>
       </c>
       <c r="K925" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48144,22 +48144,22 @@
       </c>
       <c r="B926" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C926" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEL SOL S.A.</t>
+          <t>RUFFIN ESTEBAN MAURICIO</t>
         </is>
       </c>
       <c r="D926" s="2" t="inlineStr">
         <is>
-          <t>30615571454</t>
+          <t>20264366896</t>
         </is>
       </c>
       <c r="E926" s="2" t="inlineStr">
         <is>
-          <t>00008-00020902</t>
+          <t>00002-00000229</t>
         </is>
       </c>
       <c r="F926" s="2" t="inlineStr">
@@ -48181,11 +48181,11 @@
         </is>
       </c>
       <c r="J926" s="3" t="n">
-        <v>158885.19</v>
+        <v>21864.78</v>
       </c>
       <c r="K926" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48202,26 +48202,26 @@
       </c>
       <c r="C927" s="2" t="inlineStr">
         <is>
-          <t>EQUILIBRE SALUD S.A.S.</t>
+          <t>CLINICA PRIVADA DEAN FUNES S.R.L.</t>
         </is>
       </c>
       <c r="D927" s="2" t="inlineStr">
         <is>
-          <t>33716532629</t>
+          <t>30708237791</t>
         </is>
       </c>
       <c r="E927" s="2" t="inlineStr">
         <is>
-          <t>00001-00000639</t>
+          <t>4-978</t>
         </is>
       </c>
       <c r="F927" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G927" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H927" s="2" t="inlineStr">
         <is>
@@ -48234,11 +48234,11 @@
         </is>
       </c>
       <c r="J927" s="3" t="n">
-        <v>76769</v>
+        <v>2850705.51</v>
       </c>
       <c r="K927" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48255,26 +48255,26 @@
       </c>
       <c r="C928" s="2" t="inlineStr">
         <is>
-          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
+          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
         </is>
       </c>
       <c r="D928" s="2" t="inlineStr">
         <is>
-          <t>30566278207</t>
+          <t>30708910208</t>
         </is>
       </c>
       <c r="E928" s="2" t="inlineStr">
         <is>
-          <t>00060-00000627</t>
+          <t>118-743</t>
         </is>
       </c>
       <c r="F928" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G928" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H928" s="2" t="inlineStr">
         <is>
@@ -48287,11 +48287,11 @@
         </is>
       </c>
       <c r="J928" s="3" t="n">
-        <v>34045.3</v>
+        <v>327208</v>
       </c>
       <c r="K928" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48308,26 +48308,26 @@
       </c>
       <c r="C929" s="2" t="inlineStr">
         <is>
-          <t>EQUILIBRE SALUD S.A.S.</t>
+          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
         </is>
       </c>
       <c r="D929" s="2" t="inlineStr">
         <is>
-          <t>33716532629</t>
+          <t>30708910208</t>
         </is>
       </c>
       <c r="E929" s="2" t="inlineStr">
         <is>
-          <t>00001-00000635</t>
+          <t>118-744</t>
         </is>
       </c>
       <c r="F929" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G929" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H929" s="2" t="inlineStr">
         <is>
@@ -48340,11 +48340,11 @@
         </is>
       </c>
       <c r="J929" s="3" t="n">
-        <v>17862</v>
+        <v>260629</v>
       </c>
       <c r="K929" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48356,27 +48356,27 @@
       </c>
       <c r="B930" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C930" s="2" t="inlineStr">
         <is>
-          <t>RESONANCIA MAGNETICA SRL</t>
+          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
         </is>
       </c>
       <c r="D930" s="2" t="inlineStr">
         <is>
-          <t>30694300487</t>
+          <t>30566278207</t>
         </is>
       </c>
       <c r="E930" s="2" t="inlineStr">
         <is>
-          <t>00005-00005990</t>
+          <t>00060-00000625</t>
         </is>
       </c>
       <c r="F930" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G930" s="2" t="n">
@@ -48393,11 +48393,11 @@
         </is>
       </c>
       <c r="J930" s="3" t="n">
-        <v>213934.5</v>
+        <v>21733</v>
       </c>
       <c r="K930" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48409,27 +48409,27 @@
       </c>
       <c r="B931" s="2" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C931" s="2" t="inlineStr">
         <is>
-          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
+          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
         </is>
       </c>
       <c r="D931" s="2" t="inlineStr">
         <is>
-          <t>30716142015</t>
+          <t>30660567840</t>
         </is>
       </c>
       <c r="E931" s="2" t="inlineStr">
         <is>
-          <t>00003-00000037</t>
+          <t>00010-00004117</t>
         </is>
       </c>
       <c r="F931" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G931" s="2" t="n">
@@ -48446,11 +48446,11 @@
         </is>
       </c>
       <c r="J931" s="3" t="n">
-        <v>733125</v>
+        <v>21059.44</v>
       </c>
       <c r="K931" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48467,26 +48467,26 @@
       </c>
       <c r="C932" s="2" t="inlineStr">
         <is>
-          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
+          <t>GILETTA CLAUDIA VIVIANA</t>
         </is>
       </c>
       <c r="D932" s="2" t="inlineStr">
         <is>
-          <t>30716142015</t>
+          <t>27208730768</t>
         </is>
       </c>
       <c r="E932" s="2" t="inlineStr">
         <is>
-          <t>00003-00000036</t>
+          <t>00002-00000047</t>
         </is>
       </c>
       <c r="F932" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G932" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H932" s="2" t="inlineStr">
         <is>
@@ -48499,11 +48499,11 @@
         </is>
       </c>
       <c r="J932" s="3" t="n">
-        <v>433925</v>
+        <v>441000</v>
       </c>
       <c r="K932" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48515,31 +48515,31 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>GARRONE JESICA VALERIA</t>
         </is>
       </c>
       <c r="D933" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>27256682104</t>
         </is>
       </c>
       <c r="E933" s="2" t="inlineStr">
         <is>
-          <t>00015-00006533</t>
+          <t>01001-00000128</t>
         </is>
       </c>
       <c r="F933" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G933" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H933" s="2" t="inlineStr">
         <is>
@@ -48552,11 +48552,11 @@
         </is>
       </c>
       <c r="J933" s="3" t="n">
-        <v>2976818.05</v>
+        <v>21000</v>
       </c>
       <c r="K933" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48573,17 +48573,17 @@
       </c>
       <c r="C934" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEAN FUNES S.R.L.</t>
+          <t>PROYECTOS INNOVADORES S R L</t>
         </is>
       </c>
       <c r="D934" s="2" t="inlineStr">
         <is>
-          <t>30708237791</t>
+          <t>30709702978</t>
         </is>
       </c>
       <c r="E934" s="2" t="inlineStr">
         <is>
-          <t>4-978</t>
+          <t>00002-00000100</t>
         </is>
       </c>
       <c r="F934" s="2" t="inlineStr">
@@ -48592,7 +48592,7 @@
         </is>
       </c>
       <c r="G934" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H934" s="2" t="inlineStr">
         <is>
@@ -48605,11 +48605,11 @@
         </is>
       </c>
       <c r="J934" s="3" t="n">
-        <v>2850705.51</v>
+        <v>3630000</v>
       </c>
       <c r="K934" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48626,17 +48626,17 @@
       </c>
       <c r="C935" s="2" t="inlineStr">
         <is>
-          <t>RESONANCIA MAGNETICA SRL</t>
+          <t>CEMO S.A.</t>
         </is>
       </c>
       <c r="D935" s="2" t="inlineStr">
         <is>
-          <t>30694300487</t>
+          <t>30714353493</t>
         </is>
       </c>
       <c r="E935" s="2" t="inlineStr">
         <is>
-          <t>00005-00006007</t>
+          <t>4-10213</t>
         </is>
       </c>
       <c r="F935" s="2" t="inlineStr">
@@ -48658,11 +48658,11 @@
         </is>
       </c>
       <c r="J935" s="3" t="n">
-        <v>951358.6899999999</v>
+        <v>366907.73</v>
       </c>
       <c r="K935" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48679,17 +48679,17 @@
       </c>
       <c r="C936" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
+          <t>REBERTE MARICEL EDITH</t>
         </is>
       </c>
       <c r="D936" s="2" t="inlineStr">
         <is>
-          <t>33711273129</t>
+          <t>27230899199</t>
         </is>
       </c>
       <c r="E936" s="2" t="inlineStr">
         <is>
-          <t>00004-00012965</t>
+          <t>00003-00000215</t>
         </is>
       </c>
       <c r="F936" s="2" t="inlineStr">
@@ -48698,7 +48698,7 @@
         </is>
       </c>
       <c r="G936" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H936" s="2" t="inlineStr">
         <is>
@@ -48711,11 +48711,11 @@
         </is>
       </c>
       <c r="J936" s="3" t="n">
-        <v>497747.32</v>
+        <v>216000</v>
       </c>
       <c r="K936" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48742,7 +48742,7 @@
       </c>
       <c r="E937" s="2" t="inlineStr">
         <is>
-          <t>4-10213</t>
+          <t>4-10214</t>
         </is>
       </c>
       <c r="F937" s="2" t="inlineStr">
@@ -48764,11 +48764,11 @@
         </is>
       </c>
       <c r="J937" s="3" t="n">
-        <v>366907.73</v>
+        <v>192068.07</v>
       </c>
       <c r="K937" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48795,12 +48795,12 @@
       </c>
       <c r="E938" s="2" t="inlineStr">
         <is>
-          <t>00005-00006011</t>
+          <t>00005-00005987</t>
         </is>
       </c>
       <c r="F938" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G938" s="2" t="n">
@@ -48817,11 +48817,11 @@
         </is>
       </c>
       <c r="J938" s="3" t="n">
-        <v>244925.7</v>
+        <v>142623</v>
       </c>
       <c r="K938" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48838,26 +48838,26 @@
       </c>
       <c r="C939" s="2" t="inlineStr">
         <is>
-          <t>CEMO S.A.</t>
+          <t>CLINICA PRIVADA REGIONAL S R L</t>
         </is>
       </c>
       <c r="D939" s="2" t="inlineStr">
         <is>
-          <t>30714353493</t>
+          <t>30680944691</t>
         </is>
       </c>
       <c r="E939" s="2" t="inlineStr">
         <is>
-          <t>4-10214</t>
+          <t>00007-00002712</t>
         </is>
       </c>
       <c r="F939" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G939" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H939" s="2" t="inlineStr">
         <is>
@@ -48870,11 +48870,11 @@
         </is>
       </c>
       <c r="J939" s="3" t="n">
-        <v>192068.07</v>
+        <v>60850</v>
       </c>
       <c r="K939" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48891,22 +48891,22 @@
       </c>
       <c r="C940" s="2" t="inlineStr">
         <is>
-          <t>RESONANCIA MAGNETICA SRL</t>
+          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
         </is>
       </c>
       <c r="D940" s="2" t="inlineStr">
         <is>
-          <t>30694300487</t>
+          <t>33711273129</t>
         </is>
       </c>
       <c r="E940" s="2" t="inlineStr">
         <is>
-          <t>00005-00006006</t>
+          <t>00004-00012966</t>
         </is>
       </c>
       <c r="F940" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G940" s="2" t="n">
@@ -48923,11 +48923,11 @@
         </is>
       </c>
       <c r="J940" s="3" t="n">
-        <v>83094.35000000001</v>
+        <v>56688.28</v>
       </c>
       <c r="K940" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48944,22 +48944,22 @@
       </c>
       <c r="C941" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
+          <t>SANATORIO MORRA S A</t>
         </is>
       </c>
       <c r="D941" s="2" t="inlineStr">
         <is>
-          <t>33711273129</t>
+          <t>30545879138</t>
         </is>
       </c>
       <c r="E941" s="2" t="inlineStr">
         <is>
-          <t>00004-00012966</t>
+          <t>00010-00004790</t>
         </is>
       </c>
       <c r="F941" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G941" s="2" t="n">
@@ -48976,11 +48976,11 @@
         </is>
       </c>
       <c r="J941" s="3" t="n">
-        <v>56688.28</v>
+        <v>27483.47</v>
       </c>
       <c r="K941" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -48997,17 +48997,17 @@
       </c>
       <c r="C942" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
+          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S.A.</t>
         </is>
       </c>
       <c r="D942" s="2" t="inlineStr">
         <is>
-          <t>33711273129</t>
+          <t>30546133865</t>
         </is>
       </c>
       <c r="E942" s="2" t="inlineStr">
         <is>
-          <t>00004-00012967</t>
+          <t>00008-00012002</t>
         </is>
       </c>
       <c r="F942" s="2" t="inlineStr">
@@ -49029,11 +49029,11 @@
         </is>
       </c>
       <c r="J942" s="3" t="n">
-        <v>23262.96</v>
+        <v>26094.56</v>
       </c>
       <c r="K942" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49045,22 +49045,22 @@
       </c>
       <c r="B943" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C943" s="2" t="inlineStr">
         <is>
-          <t>SICOT MELINA PAULA</t>
+          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
         </is>
       </c>
       <c r="D943" s="2" t="inlineStr">
         <is>
-          <t>27344018451</t>
+          <t>30660567840</t>
         </is>
       </c>
       <c r="E943" s="2" t="inlineStr">
         <is>
-          <t>00003-00000968</t>
+          <t>00010-00004118</t>
         </is>
       </c>
       <c r="F943" s="2" t="inlineStr">
@@ -49082,11 +49082,11 @@
         </is>
       </c>
       <c r="J943" s="3" t="n">
-        <v>68000</v>
+        <v>18105.6</v>
       </c>
       <c r="K943" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49098,27 +49098,27 @@
       </c>
       <c r="B944" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C944" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D944" s="2" t="inlineStr">
         <is>
-          <t>30608875227</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E944" s="2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>00015-00006533</t>
         </is>
       </c>
       <c r="F944" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G944" s="2" t="n">
@@ -49135,11 +49135,11 @@
         </is>
       </c>
       <c r="J944" s="3" t="n">
-        <v>2425500</v>
+        <v>2976818.05</v>
       </c>
       <c r="K944" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49156,17 +49156,17 @@
       </c>
       <c r="C945" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO PARQUE   S A</t>
+          <t>CLINICA PRIVADA DEL SOL S.A.</t>
         </is>
       </c>
       <c r="D945" s="2" t="inlineStr">
         <is>
-          <t>30562336237</t>
+          <t>30615571454</t>
         </is>
       </c>
       <c r="E945" s="2" t="inlineStr">
         <is>
-          <t>00005-00009671</t>
+          <t>8-20797</t>
         </is>
       </c>
       <c r="F945" s="2" t="inlineStr">
@@ -49175,7 +49175,7 @@
         </is>
       </c>
       <c r="G945" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H945" s="2" t="inlineStr">
         <is>
@@ -49188,11 +49188,11 @@
         </is>
       </c>
       <c r="J945" s="3" t="n">
-        <v>594222.41</v>
+        <v>2303237.09</v>
       </c>
       <c r="K945" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49209,26 +49209,26 @@
       </c>
       <c r="C946" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="D946" s="2" t="inlineStr">
         <is>
-          <t>30660567840</t>
+          <t>30689767946</t>
         </is>
       </c>
       <c r="E946" s="2" t="inlineStr">
         <is>
-          <t>00010-00004093</t>
+          <t>00015-00001507</t>
         </is>
       </c>
       <c r="F946" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G946" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H946" s="2" t="inlineStr">
         <is>
@@ -49241,11 +49241,11 @@
         </is>
       </c>
       <c r="J946" s="3" t="n">
-        <v>101976.5</v>
+        <v>1779717.61</v>
       </c>
       <c r="K946" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49262,22 +49262,22 @@
       </c>
       <c r="C947" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE ESPECIALIDADES DE VILLA MARIA S R L</t>
+          <t>CLINICA PRIVADA CARAFFA SRL</t>
         </is>
       </c>
       <c r="D947" s="2" t="inlineStr">
         <is>
-          <t>30645574326</t>
+          <t>30596272165</t>
         </is>
       </c>
       <c r="E947" s="2" t="inlineStr">
         <is>
-          <t>00004-00014004</t>
+          <t>20-54</t>
         </is>
       </c>
       <c r="F947" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G947" s="2" t="n">
@@ -49294,11 +49294,11 @@
         </is>
       </c>
       <c r="J947" s="3" t="n">
-        <v>82184.34</v>
+        <v>1365682.29</v>
       </c>
       <c r="K947" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49315,22 +49315,22 @@
       </c>
       <c r="C948" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
+          <t>CLINICA PRIVADA CARAFFA SRL</t>
         </is>
       </c>
       <c r="D948" s="2" t="inlineStr">
         <is>
-          <t>30660567840</t>
+          <t>30596272165</t>
         </is>
       </c>
       <c r="E948" s="2" t="inlineStr">
         <is>
-          <t>00010-00004117</t>
+          <t>9-3988</t>
         </is>
       </c>
       <c r="F948" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G948" s="2" t="n">
@@ -49347,11 +49347,11 @@
         </is>
       </c>
       <c r="J948" s="3" t="n">
-        <v>21059.44</v>
+        <v>725680</v>
       </c>
       <c r="K948" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49368,22 +49368,22 @@
       </c>
       <c r="C949" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
+          <t>RESONANCIA MAGNETICA SRL</t>
         </is>
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>30660567840</t>
+          <t>30694300487</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
         <is>
-          <t>00010-00004118</t>
+          <t>00005-00005990</t>
         </is>
       </c>
       <c r="F949" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G949" s="2" t="n">
@@ -49400,11 +49400,11 @@
         </is>
       </c>
       <c r="J949" s="3" t="n">
-        <v>18105.6</v>
+        <v>213934.5</v>
       </c>
       <c r="K949" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49431,12 +49431,12 @@
       </c>
       <c r="E950" s="2" t="inlineStr">
         <is>
-          <t>00010-00004103</t>
+          <t>00010-00004093</t>
         </is>
       </c>
       <c r="F950" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G950" s="2" t="n">
@@ -49453,11 +49453,11 @@
         </is>
       </c>
       <c r="J950" s="3" t="n">
-        <v>17983.88</v>
+        <v>101976.5</v>
       </c>
       <c r="K950" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49474,22 +49474,22 @@
       </c>
       <c r="C951" s="2" t="inlineStr">
         <is>
-          <t>REYLES S.A.</t>
+          <t>CLINICA PRIVADA DE ESPECIALIDADES DE VILLA MARIA S R L</t>
         </is>
       </c>
       <c r="D951" s="2" t="inlineStr">
         <is>
-          <t>30708497629</t>
+          <t>30645574326</t>
         </is>
       </c>
       <c r="E951" s="2" t="inlineStr">
         <is>
-          <t>00010-00003784</t>
+          <t>00004-00014004</t>
         </is>
       </c>
       <c r="F951" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G951" s="2" t="n">
@@ -49506,11 +49506,11 @@
         </is>
       </c>
       <c r="J951" s="3" t="n">
-        <v>9705.6</v>
+        <v>82184.34</v>
       </c>
       <c r="K951" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49522,27 +49522,27 @@
       </c>
       <c r="B952" s="2" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="C952" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
         </is>
       </c>
       <c r="D952" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>30660567840</t>
         </is>
       </c>
       <c r="E952" s="2" t="inlineStr">
         <is>
-          <t>17-13258</t>
+          <t>00010-00004103</t>
         </is>
       </c>
       <c r="F952" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G952" s="2" t="n">
@@ -49559,11 +49559,11 @@
         </is>
       </c>
       <c r="J952" s="3" t="n">
-        <v>3889601.55</v>
+        <v>17983.88</v>
       </c>
       <c r="K952" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49580,17 +49580,17 @@
       </c>
       <c r="C953" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
+          <t>CLINICA PRIVADA CARAFFA SRL</t>
         </is>
       </c>
       <c r="D953" s="2" t="inlineStr">
         <is>
-          <t>30608875227</t>
+          <t>30596272165</t>
         </is>
       </c>
       <c r="E953" s="2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>20-51</t>
         </is>
       </c>
       <c r="F953" s="2" t="inlineStr">
@@ -49612,11 +49612,11 @@
         </is>
       </c>
       <c r="J953" s="3" t="n">
-        <v>2940000</v>
+        <v>7664269.35</v>
       </c>
       <c r="K953" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49633,26 +49633,26 @@
       </c>
       <c r="C954" s="2" t="inlineStr">
         <is>
-          <t>IMAGENES MEDICAS S.R.L.</t>
+          <t>CLINICA PRIVADA DEL SOL S.A.</t>
         </is>
       </c>
       <c r="D954" s="2" t="inlineStr">
         <is>
-          <t>30689768861</t>
+          <t>30615571454</t>
         </is>
       </c>
       <c r="E954" s="2" t="inlineStr">
         <is>
-          <t>6-8782</t>
+          <t>8-20794</t>
         </is>
       </c>
       <c r="F954" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G954" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H954" s="2" t="inlineStr">
         <is>
@@ -49665,11 +49665,11 @@
         </is>
       </c>
       <c r="J954" s="3" t="n">
-        <v>1132791.13</v>
+        <v>2998785.71</v>
       </c>
       <c r="K954" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49696,7 +49696,7 @@
       </c>
       <c r="E955" s="2" t="inlineStr">
         <is>
-          <t>3-289</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="F955" s="2" t="inlineStr">
@@ -49718,11 +49718,11 @@
         </is>
       </c>
       <c r="J955" s="3" t="n">
-        <v>981925</v>
+        <v>2940000</v>
       </c>
       <c r="K955" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49739,17 +49739,17 @@
       </c>
       <c r="C956" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA CARAFFA SRL</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D956" s="2" t="inlineStr">
         <is>
-          <t>30596272165</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E956" s="2" t="inlineStr">
         <is>
-          <t>9-3988</t>
+          <t>00015-00006514</t>
         </is>
       </c>
       <c r="F956" s="2" t="inlineStr">
@@ -49771,11 +49771,11 @@
         </is>
       </c>
       <c r="J956" s="3" t="n">
-        <v>725680</v>
+        <v>1973505.76</v>
       </c>
       <c r="K956" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49792,17 +49792,17 @@
       </c>
       <c r="C957" s="2" t="inlineStr">
         <is>
-          <t>COSEME SA</t>
+          <t>IMAGENES MEDICAS S.R.L.</t>
         </is>
       </c>
       <c r="D957" s="2" t="inlineStr">
         <is>
-          <t>30680565224</t>
+          <t>30689768861</t>
         </is>
       </c>
       <c r="E957" s="2" t="inlineStr">
         <is>
-          <t>00047-00001942</t>
+          <t>6-8782</t>
         </is>
       </c>
       <c r="F957" s="2" t="inlineStr">
@@ -49824,7 +49824,7 @@
         </is>
       </c>
       <c r="J957" s="3" t="n">
-        <v>718992.42</v>
+        <v>1132791.13</v>
       </c>
       <c r="K957" s="2" t="inlineStr">
         <is>
@@ -49845,26 +49845,26 @@
       </c>
       <c r="C958" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="D958" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>30689767946</t>
         </is>
       </c>
       <c r="E958" s="2" t="inlineStr">
         <is>
-          <t>29-3593</t>
+          <t>00015-00001646</t>
         </is>
       </c>
       <c r="F958" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G958" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H958" s="2" t="inlineStr">
         <is>
@@ -49877,11 +49877,11 @@
         </is>
       </c>
       <c r="J958" s="3" t="n">
-        <v>392650</v>
+        <v>453371.83</v>
       </c>
       <c r="K958" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49898,17 +49898,17 @@
       </c>
       <c r="C959" s="2" t="inlineStr">
         <is>
-          <t>COSEME SA</t>
+          <t>SANCHEZ LUIS FERNANDO</t>
         </is>
       </c>
       <c r="D959" s="2" t="inlineStr">
         <is>
-          <t>30680565224</t>
+          <t>20927934281</t>
         </is>
       </c>
       <c r="E959" s="2" t="inlineStr">
         <is>
-          <t>00046-00004610</t>
+          <t>00002-00000163</t>
         </is>
       </c>
       <c r="F959" s="2" t="inlineStr">
@@ -49917,7 +49917,7 @@
         </is>
       </c>
       <c r="G959" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H959" s="2" t="inlineStr">
         <is>
@@ -49930,11 +49930,11 @@
         </is>
       </c>
       <c r="J959" s="3" t="n">
-        <v>267595.91</v>
+        <v>260000</v>
       </c>
       <c r="K959" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -49951,17 +49951,17 @@
       </c>
       <c r="C960" s="2" t="inlineStr">
         <is>
-          <t>BARIATRICA S.A. S. A.</t>
+          <t>GRUPO OPTICO SA</t>
         </is>
       </c>
       <c r="D960" s="2" t="inlineStr">
         <is>
-          <t>30709634964</t>
+          <t>30709290866</t>
         </is>
       </c>
       <c r="E960" s="2" t="inlineStr">
         <is>
-          <t>00002-00001226</t>
+          <t>15-5180</t>
         </is>
       </c>
       <c r="F960" s="2" t="inlineStr">
@@ -49970,7 +49970,7 @@
         </is>
       </c>
       <c r="G960" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H960" s="2" t="inlineStr">
         <is>
@@ -49983,11 +49983,11 @@
         </is>
       </c>
       <c r="J960" s="3" t="n">
-        <v>86790</v>
+        <v>216720</v>
       </c>
       <c r="K960" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50040,7 +50040,7 @@
       </c>
       <c r="K961" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50057,17 +50057,17 @@
       </c>
       <c r="C962" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO PARQUE   S A</t>
+          <t>BARIATRICA S.A. S. A.</t>
         </is>
       </c>
       <c r="D962" s="2" t="inlineStr">
         <is>
-          <t>30562336237</t>
+          <t>30709634964</t>
         </is>
       </c>
       <c r="E962" s="2" t="inlineStr">
         <is>
-          <t>00005-00009690</t>
+          <t>00002-00001226</t>
         </is>
       </c>
       <c r="F962" s="2" t="inlineStr">
@@ -50089,11 +50089,11 @@
         </is>
       </c>
       <c r="J962" s="3" t="n">
-        <v>83316</v>
+        <v>86790</v>
       </c>
       <c r="K962" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50110,26 +50110,26 @@
       </c>
       <c r="C963" s="2" t="inlineStr">
         <is>
-          <t>COSEME SA</t>
+          <t>COLEGIO PSICOLOGOS DE LA PROV. DE CORDOBA</t>
         </is>
       </c>
       <c r="D963" s="2" t="inlineStr">
         <is>
-          <t>30680565224</t>
+          <t>30680948891</t>
         </is>
       </c>
       <c r="E963" s="2" t="inlineStr">
         <is>
-          <t>00046-00004607</t>
+          <t>000012-0000851</t>
         </is>
       </c>
       <c r="F963" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G963" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H963" s="2" t="inlineStr">
         <is>
@@ -50142,11 +50142,11 @@
         </is>
       </c>
       <c r="J963" s="3" t="n">
-        <v>20945.33</v>
+        <v>78624</v>
       </c>
       <c r="K963" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50158,31 +50158,31 @@
       </c>
       <c r="B964" s="2" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="C964" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>COLEGIO MEDICO REGIONAL ARROYITO</t>
         </is>
       </c>
       <c r="D964" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30555217419</t>
         </is>
       </c>
       <c r="E964" s="2" t="inlineStr">
         <is>
-          <t>00024-00023158</t>
+          <t>00004-00009702</t>
         </is>
       </c>
       <c r="F964" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G964" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H964" s="2" t="inlineStr">
         <is>
@@ -50195,11 +50195,11 @@
         </is>
       </c>
       <c r="J964" s="3" t="n">
-        <v>16638208.85</v>
+        <v>53488.34</v>
       </c>
       <c r="K964" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50211,27 +50211,27 @@
       </c>
       <c r="B965" s="2" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="C965" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>COSEME SA</t>
         </is>
       </c>
       <c r="D965" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30680565224</t>
         </is>
       </c>
       <c r="E965" s="2" t="inlineStr">
         <is>
-          <t>00024-00023155</t>
+          <t>00046-00004607</t>
         </is>
       </c>
       <c r="F965" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G965" s="2" t="n">
@@ -50248,11 +50248,11 @@
         </is>
       </c>
       <c r="J965" s="3" t="n">
-        <v>10391656.65</v>
+        <v>20945.33</v>
       </c>
       <c r="K965" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50269,17 +50269,17 @@
       </c>
       <c r="C966" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA CARAFFA SRL</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D966" s="2" t="inlineStr">
         <is>
-          <t>30596272165</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E966" s="2" t="inlineStr">
         <is>
-          <t>20-51</t>
+          <t>42-190</t>
         </is>
       </c>
       <c r="F966" s="2" t="inlineStr">
@@ -50301,11 +50301,11 @@
         </is>
       </c>
       <c r="J966" s="3" t="n">
-        <v>7664269.35</v>
+        <v>20645230.11</v>
       </c>
       <c r="K966" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50332,12 +50332,12 @@
       </c>
       <c r="E967" s="2" t="inlineStr">
         <is>
-          <t>00024-00023154</t>
+          <t>00024-00023158</t>
         </is>
       </c>
       <c r="F967" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G967" s="2" t="n">
@@ -50354,11 +50354,11 @@
         </is>
       </c>
       <c r="J967" s="3" t="n">
-        <v>5230519.21</v>
+        <v>16638208.85</v>
       </c>
       <c r="K967" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50411,7 +50411,7 @@
       </c>
       <c r="K968" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50438,7 +50438,7 @@
       </c>
       <c r="E969" s="2" t="inlineStr">
         <is>
-          <t>42-180</t>
+          <t>17-13258</t>
         </is>
       </c>
       <c r="F969" s="2" t="inlineStr">
@@ -50460,11 +50460,11 @@
         </is>
       </c>
       <c r="J969" s="3" t="n">
-        <v>3065538.44</v>
+        <v>3889601.55</v>
       </c>
       <c r="K969" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50481,17 +50481,17 @@
       </c>
       <c r="C970" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA CARAFFA SRL</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D970" s="2" t="inlineStr">
         <is>
-          <t>30596272165</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E970" s="2" t="inlineStr">
         <is>
-          <t>20-54</t>
+          <t>42-180</t>
         </is>
       </c>
       <c r="F970" s="2" t="inlineStr">
@@ -50513,11 +50513,11 @@
         </is>
       </c>
       <c r="J970" s="3" t="n">
-        <v>1365682.29</v>
+        <v>3065538.44</v>
       </c>
       <c r="K970" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50534,17 +50534,17 @@
       </c>
       <c r="C971" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
         </is>
       </c>
       <c r="D971" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30608875227</t>
         </is>
       </c>
       <c r="E971" s="2" t="inlineStr">
         <is>
-          <t>00024-00023159</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="F971" s="2" t="inlineStr">
@@ -50566,11 +50566,11 @@
         </is>
       </c>
       <c r="J971" s="3" t="n">
-        <v>952729.96</v>
+        <v>2425500</v>
       </c>
       <c r="K971" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50587,17 +50587,17 @@
       </c>
       <c r="C972" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D972" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E972" s="2" t="inlineStr">
         <is>
-          <t>00024-00023177</t>
+          <t>42-204</t>
         </is>
       </c>
       <c r="F972" s="2" t="inlineStr">
@@ -50619,11 +50619,11 @@
         </is>
       </c>
       <c r="J972" s="3" t="n">
-        <v>725065.77</v>
+        <v>2392436.15</v>
       </c>
       <c r="K972" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50640,17 +50640,17 @@
       </c>
       <c r="C973" s="2" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PRIVADO SAN ANDRES SRL</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D973" s="2" t="inlineStr">
         <is>
-          <t>30715347756</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E973" s="2" t="inlineStr">
         <is>
-          <t>00001-00004059</t>
+          <t>00024-00023159</t>
         </is>
       </c>
       <c r="F973" s="2" t="inlineStr">
@@ -50672,11 +50672,11 @@
         </is>
       </c>
       <c r="J973" s="3" t="n">
-        <v>466174.9</v>
+        <v>952729.96</v>
       </c>
       <c r="K973" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50693,17 +50693,17 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>UNIDAD DIGESTIVA BAISTROCCHI S.R.L.</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr">
         <is>
-          <t>30711999074</t>
+          <t>30689767946</t>
         </is>
       </c>
       <c r="E974" s="2" t="inlineStr">
         <is>
-          <t>3-2018</t>
+          <t>00015-00001505</t>
         </is>
       </c>
       <c r="F974" s="2" t="inlineStr">
@@ -50712,7 +50712,7 @@
         </is>
       </c>
       <c r="G974" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H974" s="2" t="inlineStr">
         <is>
@@ -50725,11 +50725,11 @@
         </is>
       </c>
       <c r="J974" s="3" t="n">
-        <v>347600</v>
+        <v>774958.7</v>
       </c>
       <c r="K974" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50746,17 +50746,17 @@
       </c>
       <c r="C975" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>SANATORIO PARQUE   S A</t>
         </is>
       </c>
       <c r="D975" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30562336237</t>
         </is>
       </c>
       <c r="E975" s="2" t="inlineStr">
         <is>
-          <t>00024-00023156</t>
+          <t>00005-00009671</t>
         </is>
       </c>
       <c r="F975" s="2" t="inlineStr">
@@ -50778,11 +50778,11 @@
         </is>
       </c>
       <c r="J975" s="3" t="n">
-        <v>324557.81</v>
+        <v>594222.41</v>
       </c>
       <c r="K975" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50799,17 +50799,17 @@
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>SOLBO S.A.S.</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30716784386</t>
         </is>
       </c>
       <c r="E976" s="2" t="inlineStr">
         <is>
-          <t>00024-00023178</t>
+          <t>1-468</t>
         </is>
       </c>
       <c r="F976" s="2" t="inlineStr">
@@ -50831,11 +50831,11 @@
         </is>
       </c>
       <c r="J976" s="3" t="n">
-        <v>276888.6</v>
+        <v>470899.34</v>
       </c>
       <c r="K976" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50852,22 +50852,22 @@
       </c>
       <c r="C977" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
+          <t>CENTRO MEDICO PRIVADO SAN ANDRES SRL</t>
         </is>
       </c>
       <c r="D977" s="2" t="inlineStr">
         <is>
-          <t>30608875227</t>
+          <t>30715347756</t>
         </is>
       </c>
       <c r="E977" s="2" t="inlineStr">
         <is>
-          <t>3-296</t>
+          <t>00001-00004059</t>
         </is>
       </c>
       <c r="F977" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G977" s="2" t="n">
@@ -50884,11 +50884,11 @@
         </is>
       </c>
       <c r="J977" s="3" t="n">
-        <v>215775</v>
+        <v>466174.9</v>
       </c>
       <c r="K977" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50905,22 +50905,22 @@
       </c>
       <c r="C978" s="2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
         </is>
       </c>
       <c r="D978" s="2" t="inlineStr">
         <is>
-          <t>30545894528</t>
+          <t>30716142015</t>
         </is>
       </c>
       <c r="E978" s="2" t="inlineStr">
         <is>
-          <t>00024-00023176</t>
+          <t>00003-00000036</t>
         </is>
       </c>
       <c r="F978" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G978" s="2" t="n">
@@ -50937,11 +50937,11 @@
         </is>
       </c>
       <c r="J978" s="3" t="n">
-        <v>187926.14</v>
+        <v>433925</v>
       </c>
       <c r="K978" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -50958,17 +50958,17 @@
       </c>
       <c r="C979" s="2" t="inlineStr">
         <is>
-          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="D979" s="2" t="inlineStr">
         <is>
-          <t>30716142015</t>
+          <t>30645189988</t>
         </is>
       </c>
       <c r="E979" s="2" t="inlineStr">
         <is>
-          <t>00003-00000048</t>
+          <t>29-3593</t>
         </is>
       </c>
       <c r="F979" s="2" t="inlineStr">
@@ -50990,11 +50990,11 @@
         </is>
       </c>
       <c r="J979" s="3" t="n">
-        <v>51536</v>
+        <v>392650</v>
       </c>
       <c r="K979" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51011,17 +51011,17 @@
       </c>
       <c r="C980" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO MORRA S A</t>
+          <t>CLINICA CHUTRO S R L</t>
         </is>
       </c>
       <c r="D980" s="2" t="inlineStr">
         <is>
-          <t>30545879138</t>
+          <t>30545996991</t>
         </is>
       </c>
       <c r="E980" s="2" t="inlineStr">
         <is>
-          <t>00010-00004790</t>
+          <t>00004-00006085</t>
         </is>
       </c>
       <c r="F980" s="2" t="inlineStr">
@@ -51043,11 +51043,11 @@
         </is>
       </c>
       <c r="J980" s="3" t="n">
-        <v>27483.47</v>
+        <v>392263.88</v>
       </c>
       <c r="K980" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51059,22 +51059,22 @@
       </c>
       <c r="B981" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="C981" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>UNIDAD DIGESTIVA BAISTROCCHI S.R.L.</t>
         </is>
       </c>
       <c r="D981" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>30711999074</t>
         </is>
       </c>
       <c r="E981" s="2" t="inlineStr">
         <is>
-          <t>42-190</t>
+          <t>3-2018</t>
         </is>
       </c>
       <c r="F981" s="2" t="inlineStr">
@@ -51096,7 +51096,7 @@
         </is>
       </c>
       <c r="J981" s="3" t="n">
-        <v>20645230.11</v>
+        <v>347600</v>
       </c>
       <c r="K981" s="2" t="inlineStr">
         <is>
@@ -51112,27 +51112,27 @@
       </c>
       <c r="B982" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="C982" s="2" t="inlineStr">
         <is>
-          <t>CIPREM SRL</t>
+          <t>CLINICA CHUTRO S R L</t>
         </is>
       </c>
       <c r="D982" s="2" t="inlineStr">
         <is>
-          <t>30637580961</t>
+          <t>30545996991</t>
         </is>
       </c>
       <c r="E982" s="2" t="inlineStr">
         <is>
-          <t>00004-00014771</t>
+          <t>00004-00006086</t>
         </is>
       </c>
       <c r="F982" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G982" s="2" t="n">
@@ -51149,11 +51149,11 @@
         </is>
       </c>
       <c r="J982" s="3" t="n">
-        <v>9446523.82</v>
+        <v>160910.1</v>
       </c>
       <c r="K982" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51165,27 +51165,27 @@
       </c>
       <c r="B983" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="C983" s="2" t="inlineStr">
         <is>
-          <t>ESTIX S.A.S.</t>
+          <t>SICOT MELINA PAULA</t>
         </is>
       </c>
       <c r="D983" s="2" t="inlineStr">
         <is>
-          <t>30717147835</t>
+          <t>27344018451</t>
         </is>
       </c>
       <c r="E983" s="2" t="inlineStr">
         <is>
-          <t>4-471</t>
+          <t>00003-00000968</t>
         </is>
       </c>
       <c r="F983" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G983" s="2" t="n">
@@ -51202,11 +51202,11 @@
         </is>
       </c>
       <c r="J983" s="3" t="n">
-        <v>528390.64</v>
+        <v>68000</v>
       </c>
       <c r="K983" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51223,22 +51223,22 @@
       </c>
       <c r="C984" s="2" t="inlineStr">
         <is>
-          <t>SANATORIO MORRA S A</t>
+          <t>CIPREM SRL</t>
         </is>
       </c>
       <c r="D984" s="2" t="inlineStr">
         <is>
-          <t>30545879138</t>
+          <t>30637580961</t>
         </is>
       </c>
       <c r="E984" s="2" t="inlineStr">
         <is>
-          <t>00010-00004828</t>
+          <t>00004-00014771</t>
         </is>
       </c>
       <c r="F984" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G984" s="2" t="n">
@@ -51255,11 +51255,11 @@
         </is>
       </c>
       <c r="J984" s="3" t="n">
-        <v>442224.5</v>
+        <v>9446523.82</v>
       </c>
       <c r="K984" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51276,17 +51276,17 @@
       </c>
       <c r="C985" s="2" t="inlineStr">
         <is>
-          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
+          <t>ECCO S. A. U.</t>
         </is>
       </c>
       <c r="D985" s="2" t="inlineStr">
         <is>
-          <t>30708910208</t>
+          <t>30602764032</t>
         </is>
       </c>
       <c r="E985" s="2" t="inlineStr">
         <is>
-          <t>118-743</t>
+          <t>203-162147</t>
         </is>
       </c>
       <c r="F985" s="2" t="inlineStr">
@@ -51295,7 +51295,7 @@
         </is>
       </c>
       <c r="G985" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H985" s="2" t="inlineStr">
         <is>
@@ -51308,11 +51308,11 @@
         </is>
       </c>
       <c r="J985" s="3" t="n">
-        <v>327208</v>
+        <v>3996654.02</v>
       </c>
       <c r="K985" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51329,22 +51329,22 @@
       </c>
       <c r="C986" s="2" t="inlineStr">
         <is>
-          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
+          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
         </is>
       </c>
       <c r="D986" s="2" t="inlineStr">
         <is>
-          <t>30708910208</t>
+          <t>30608875227</t>
         </is>
       </c>
       <c r="E986" s="2" t="inlineStr">
         <is>
-          <t>118-744</t>
+          <t>3-289</t>
         </is>
       </c>
       <c r="F986" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G986" s="2" t="n">
@@ -51361,11 +51361,11 @@
         </is>
       </c>
       <c r="J986" s="3" t="n">
-        <v>260629</v>
+        <v>981925</v>
       </c>
       <c r="K986" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51382,17 +51382,17 @@
       </c>
       <c r="C987" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S.A.</t>
+          <t>EDUARDO JORGE LOYEAU</t>
         </is>
       </c>
       <c r="D987" s="2" t="inlineStr">
         <is>
-          <t>30546133865</t>
+          <t>20101728820</t>
         </is>
       </c>
       <c r="E987" s="2" t="inlineStr">
         <is>
-          <t>00008-00012005</t>
+          <t>2-178</t>
         </is>
       </c>
       <c r="F987" s="2" t="inlineStr">
@@ -51401,7 +51401,7 @@
         </is>
       </c>
       <c r="G987" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H987" s="2" t="inlineStr">
         <is>
@@ -51414,11 +51414,11 @@
         </is>
       </c>
       <c r="J987" s="3" t="n">
-        <v>205601.57</v>
+        <v>825000</v>
       </c>
       <c r="K987" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51435,22 +51435,22 @@
       </c>
       <c r="C988" s="2" t="inlineStr">
         <is>
-          <t>CIPREM SRL</t>
+          <t>SANATORIO MORRA S A</t>
         </is>
       </c>
       <c r="D988" s="2" t="inlineStr">
         <is>
-          <t>30637580961</t>
+          <t>30545879138</t>
         </is>
       </c>
       <c r="E988" s="2" t="inlineStr">
         <is>
-          <t>00004-00014773</t>
+          <t>00010-00004828</t>
         </is>
       </c>
       <c r="F988" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G988" s="2" t="n">
@@ -51467,11 +51467,11 @@
         </is>
       </c>
       <c r="J988" s="3" t="n">
-        <v>67148.64</v>
+        <v>442224.5</v>
       </c>
       <c r="K988" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51488,22 +51488,22 @@
       </c>
       <c r="C989" s="2" t="inlineStr">
         <is>
-          <t>CIPREM SRL</t>
+          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLAS SRL</t>
         </is>
       </c>
       <c r="D989" s="2" t="inlineStr">
         <is>
-          <t>30637580961</t>
+          <t>30608875227</t>
         </is>
       </c>
       <c r="E989" s="2" t="inlineStr">
         <is>
-          <t>00004-00014774</t>
+          <t>3-296</t>
         </is>
       </c>
       <c r="F989" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G989" s="2" t="n">
@@ -51520,11 +51520,11 @@
         </is>
       </c>
       <c r="J989" s="3" t="n">
-        <v>42760</v>
+        <v>215775</v>
       </c>
       <c r="K989" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51541,26 +51541,26 @@
       </c>
       <c r="C990" s="2" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S.A.</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="D990" s="2" t="inlineStr">
         <is>
-          <t>30546133865</t>
+          <t>30689767946</t>
         </is>
       </c>
       <c r="E990" s="2" t="inlineStr">
         <is>
-          <t>00008-00012002</t>
+          <t>00015-00001506</t>
         </is>
       </c>
       <c r="F990" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G990" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H990" s="2" t="inlineStr">
         <is>
@@ -51573,11 +51573,11 @@
         </is>
       </c>
       <c r="J990" s="3" t="n">
-        <v>26094.56</v>
+        <v>163500.39</v>
       </c>
       <c r="K990" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51589,31 +51589,31 @@
       </c>
       <c r="B991" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C991" s="2" t="inlineStr">
         <is>
-          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
+          <t>EQUILIBRE SALUD S.A.S.</t>
         </is>
       </c>
       <c r="D991" s="2" t="inlineStr">
         <is>
-          <t>30715649159</t>
+          <t>33716532629</t>
         </is>
       </c>
       <c r="E991" s="2" t="inlineStr">
         <is>
-          <t>5-1618</t>
+          <t>00001-00000639</t>
         </is>
       </c>
       <c r="F991" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G991" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H991" s="2" t="inlineStr">
         <is>
@@ -51626,11 +51626,11 @@
         </is>
       </c>
       <c r="J991" s="3" t="n">
-        <v>29693479.22</v>
+        <v>76769</v>
       </c>
       <c r="K991" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51642,22 +51642,22 @@
       </c>
       <c r="B992" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C992" s="2" t="inlineStr">
         <is>
-          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
+          <t>CIPREM SRL</t>
         </is>
       </c>
       <c r="D992" s="2" t="inlineStr">
         <is>
-          <t>30566278207</t>
+          <t>30637580961</t>
         </is>
       </c>
       <c r="E992" s="2" t="inlineStr">
         <is>
-          <t>00060-00000622</t>
+          <t>00004-00014773</t>
         </is>
       </c>
       <c r="F992" s="2" t="inlineStr">
@@ -51679,11 +51679,11 @@
         </is>
       </c>
       <c r="J992" s="3" t="n">
-        <v>3017142.8</v>
+        <v>67148.64</v>
       </c>
       <c r="K992" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51695,22 +51695,22 @@
       </c>
       <c r="B993" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C993" s="2" t="inlineStr">
         <is>
-          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
+          <t>CIPREM SRL</t>
         </is>
       </c>
       <c r="D993" s="2" t="inlineStr">
         <is>
-          <t>30715649159</t>
+          <t>30637580961</t>
         </is>
       </c>
       <c r="E993" s="2" t="inlineStr">
         <is>
-          <t>5-1619</t>
+          <t>00004-00014774</t>
         </is>
       </c>
       <c r="F993" s="2" t="inlineStr">
@@ -51732,11 +51732,11 @@
         </is>
       </c>
       <c r="J993" s="3" t="n">
-        <v>2512406.33</v>
+        <v>42760</v>
       </c>
       <c r="K993" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51753,22 +51753,22 @@
       </c>
       <c r="C994" s="2" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
         </is>
       </c>
       <c r="D994" s="2" t="inlineStr">
         <is>
-          <t>30645189988</t>
+          <t>30715649159</t>
         </is>
       </c>
       <c r="E994" s="2" t="inlineStr">
         <is>
-          <t>42-204</t>
+          <t>5-1618</t>
         </is>
       </c>
       <c r="F994" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G994" s="2" t="n">
@@ -51785,11 +51785,11 @@
         </is>
       </c>
       <c r="J994" s="3" t="n">
-        <v>2392436.15</v>
+        <v>29693479.22</v>
       </c>
       <c r="K994" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51816,12 +51816,12 @@
       </c>
       <c r="E995" s="2" t="inlineStr">
         <is>
-          <t>00060-00000623</t>
+          <t>00060-00000622</t>
         </is>
       </c>
       <c r="F995" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G995" s="2" t="n">
@@ -51838,11 +51838,11 @@
         </is>
       </c>
       <c r="J995" s="3" t="n">
-        <v>1499370.08</v>
+        <v>3017142.8</v>
       </c>
       <c r="K995" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51869,12 +51869,12 @@
       </c>
       <c r="E996" s="2" t="inlineStr">
         <is>
-          <t>5-1627</t>
+          <t>5-1619</t>
         </is>
       </c>
       <c r="F996" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G996" s="2" t="n">
@@ -51891,11 +51891,11 @@
         </is>
       </c>
       <c r="J996" s="3" t="n">
-        <v>521987.87</v>
+        <v>2512406.33</v>
       </c>
       <c r="K996" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51912,22 +51912,22 @@
       </c>
       <c r="C997" s="2" t="inlineStr">
         <is>
-          <t>CIPREM SRL</t>
+          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
         </is>
       </c>
       <c r="D997" s="2" t="inlineStr">
         <is>
-          <t>30637580961</t>
+          <t>30566278207</t>
         </is>
       </c>
       <c r="E997" s="2" t="inlineStr">
         <is>
-          <t>00004-00014801</t>
+          <t>00060-00000623</t>
         </is>
       </c>
       <c r="F997" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G997" s="2" t="n">
@@ -51944,11 +51944,11 @@
         </is>
       </c>
       <c r="J997" s="3" t="n">
-        <v>419223.26</v>
+        <v>1499370.08</v>
       </c>
       <c r="K997" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -51975,12 +51975,12 @@
       </c>
       <c r="E998" s="2" t="inlineStr">
         <is>
-          <t>00003-00000050</t>
+          <t>00003-00000037</t>
         </is>
       </c>
       <c r="F998" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G998" s="2" t="n">
@@ -51997,11 +51997,11 @@
         </is>
       </c>
       <c r="J998" s="3" t="n">
-        <v>368144</v>
+        <v>733125</v>
       </c>
       <c r="K998" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52018,22 +52018,22 @@
       </c>
       <c r="C999" s="2" t="inlineStr">
         <is>
-          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+          <t>COSEME SA</t>
         </is>
       </c>
       <c r="D999" s="2" t="inlineStr">
         <is>
-          <t>30623442566</t>
+          <t>30680565224</t>
         </is>
       </c>
       <c r="E999" s="2" t="inlineStr">
         <is>
-          <t>00004-00015613</t>
+          <t>00047-00001942</t>
         </is>
       </c>
       <c r="F999" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G999" s="2" t="n">
@@ -52050,11 +52050,11 @@
         </is>
       </c>
       <c r="J999" s="3" t="n">
-        <v>171810.37</v>
+        <v>718992.42</v>
       </c>
       <c r="K999" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52071,22 +52071,22 @@
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>LECOUSER S.A.</t>
+          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr">
         <is>
-          <t>33717029009</t>
+          <t>30715649159</t>
         </is>
       </c>
       <c r="E1000" s="2" t="inlineStr">
         <is>
-          <t>00001-00001004</t>
+          <t>5-1627</t>
         </is>
       </c>
       <c r="F1000" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G1000" s="2" t="n">
@@ -52103,11 +52103,11 @@
         </is>
       </c>
       <c r="J1000" s="3" t="n">
-        <v>165000</v>
+        <v>521987.87</v>
       </c>
       <c r="K1000" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52124,22 +52124,22 @@
       </c>
       <c r="C1001" s="2" t="inlineStr">
         <is>
-          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+          <t>CIPREM SRL</t>
         </is>
       </c>
       <c r="D1001" s="2" t="inlineStr">
         <is>
-          <t>30623442566</t>
+          <t>30637580961</t>
         </is>
       </c>
       <c r="E1001" s="2" t="inlineStr">
         <is>
-          <t>00004-00015616</t>
+          <t>00004-00014801</t>
         </is>
       </c>
       <c r="F1001" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1001" s="2" t="n">
@@ -52156,11 +52156,11 @@
         </is>
       </c>
       <c r="J1001" s="3" t="n">
-        <v>149262.05</v>
+        <v>419223.26</v>
       </c>
       <c r="K1001" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52177,22 +52177,22 @@
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+          <t>COSEME SA</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr">
         <is>
-          <t>30623442566</t>
+          <t>30680565224</t>
         </is>
       </c>
       <c r="E1002" s="2" t="inlineStr">
         <is>
-          <t>00004-00015612</t>
+          <t>00046-00004610</t>
         </is>
       </c>
       <c r="F1002" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1002" s="2" t="n">
@@ -52209,11 +52209,11 @@
         </is>
       </c>
       <c r="J1002" s="3" t="n">
-        <v>91850.56</v>
+        <v>267595.91</v>
       </c>
       <c r="K1002" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52240,12 +52240,12 @@
       </c>
       <c r="E1003" s="2" t="inlineStr">
         <is>
-          <t>00004-00015611</t>
+          <t>00004-00015613</t>
         </is>
       </c>
       <c r="F1003" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G1003" s="2" t="n">
@@ -52262,11 +52262,11 @@
         </is>
       </c>
       <c r="J1003" s="3" t="n">
-        <v>87524.03999999999</v>
+        <v>171810.37</v>
       </c>
       <c r="K1003" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="E1004" s="2" t="inlineStr">
         <is>
-          <t>00004-00015615</t>
+          <t>00004-00015616</t>
         </is>
       </c>
       <c r="F1004" s="2" t="inlineStr">
@@ -52315,11 +52315,11 @@
         </is>
       </c>
       <c r="J1004" s="3" t="n">
-        <v>78412.84</v>
+        <v>149262.05</v>
       </c>
       <c r="K1004" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52346,7 +52346,7 @@
       </c>
       <c r="E1005" s="2" t="inlineStr">
         <is>
-          <t>00004-00015614</t>
+          <t>00004-00015612</t>
         </is>
       </c>
       <c r="F1005" s="2" t="inlineStr">
@@ -52368,11 +52368,11 @@
         </is>
       </c>
       <c r="J1005" s="3" t="n">
-        <v>65717.86</v>
+        <v>91850.56</v>
       </c>
       <c r="K1005" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52389,22 +52389,22 @@
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
+          <t>SANATORIO PARQUE   S A</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr">
         <is>
-          <t>30566278207</t>
+          <t>30562336237</t>
         </is>
       </c>
       <c r="E1006" s="2" t="inlineStr">
         <is>
-          <t>00060-00000624</t>
+          <t>00005-00009690</t>
         </is>
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1006" s="2" t="n">
@@ -52421,11 +52421,11 @@
         </is>
       </c>
       <c r="J1006" s="3" t="n">
-        <v>60267.42</v>
+        <v>83316</v>
       </c>
       <c r="K1006" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52452,12 +52452,12 @@
       </c>
       <c r="E1007" s="2" t="inlineStr">
         <is>
-          <t>00004-00015610</t>
+          <t>00004-00015615</t>
         </is>
       </c>
       <c r="F1007" s="2" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
       <c r="G1007" s="2" t="n">
@@ -52474,11 +52474,11 @@
         </is>
       </c>
       <c r="J1007" s="3" t="n">
-        <v>38125.92</v>
+        <v>78412.84</v>
       </c>
       <c r="K1007" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52495,26 +52495,26 @@
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
+          <t>L A C E SA</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr">
         <is>
-          <t>30566278207</t>
+          <t>30698488677</t>
         </is>
       </c>
       <c r="E1008" s="2" t="inlineStr">
         <is>
-          <t>00060-00000625</t>
+          <t>00082-00002028</t>
         </is>
       </c>
       <c r="F1008" s="2" t="inlineStr">
         <is>
-          <t>OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1008" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H1008" s="2" t="inlineStr">
         <is>
@@ -52527,11 +52527,11 @@
         </is>
       </c>
       <c r="J1008" s="3" t="n">
-        <v>21733</v>
+        <v>69897.60000000001</v>
       </c>
       <c r="K1008" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52543,27 +52543,27 @@
       </c>
       <c r="B1009" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C1009" s="2" t="inlineStr">
         <is>
-          <t>UROLIT SA</t>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
         </is>
       </c>
       <c r="D1009" s="2" t="inlineStr">
         <is>
-          <t>30703378222</t>
+          <t>30623442566</t>
         </is>
       </c>
       <c r="E1009" s="2" t="inlineStr">
         <is>
-          <t>3-4723</t>
+          <t>00004-00015614</t>
         </is>
       </c>
       <c r="F1009" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G1009" s="2" t="n">
@@ -52580,11 +52580,11 @@
         </is>
       </c>
       <c r="J1009" s="3" t="n">
-        <v>987646</v>
+        <v>65717.86</v>
       </c>
       <c r="K1009" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52596,27 +52596,27 @@
       </c>
       <c r="B1010" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>SOLBO S.A.S.</t>
+          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr">
         <is>
-          <t>30716784386</t>
+          <t>30566278207</t>
         </is>
       </c>
       <c r="E1010" s="2" t="inlineStr">
         <is>
-          <t>1-468</t>
+          <t>00060-00000624</t>
         </is>
       </c>
       <c r="F1010" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
       <c r="G1010" s="2" t="n">
@@ -52633,11 +52633,11 @@
         </is>
       </c>
       <c r="J1010" s="3" t="n">
-        <v>470899.34</v>
+        <v>60267.42</v>
       </c>
       <c r="K1010" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52654,17 +52654,17 @@
       </c>
       <c r="C1011" s="2" t="inlineStr">
         <is>
-          <t>SOLBO S.A.S.</t>
+          <t>SOP S R L</t>
         </is>
       </c>
       <c r="D1011" s="2" t="inlineStr">
         <is>
-          <t>30716784386</t>
+          <t>30681218285</t>
         </is>
       </c>
       <c r="E1011" s="2" t="inlineStr">
         <is>
-          <t>1-465</t>
+          <t>00009-00011612</t>
         </is>
       </c>
       <c r="F1011" s="2" t="inlineStr">
@@ -52673,7 +52673,7 @@
         </is>
       </c>
       <c r="G1011" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H1011" s="2" t="inlineStr">
         <is>
@@ -52686,11 +52686,11 @@
         </is>
       </c>
       <c r="J1011" s="3" t="n">
-        <v>334475.69</v>
+        <v>1640472</v>
       </c>
       <c r="K1011" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52702,27 +52702,27 @@
       </c>
       <c r="B1012" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>CLINICA CHUTRO S R L</t>
+          <t>UROLIT SA</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr">
         <is>
-          <t>30545996991</t>
+          <t>30703378222</t>
         </is>
       </c>
       <c r="E1012" s="2" t="inlineStr">
         <is>
-          <t>00004-00006085</t>
+          <t>3-4723</t>
         </is>
       </c>
       <c r="F1012" s="2" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1012" s="2" t="n">
@@ -52739,7 +52739,7 @@
         </is>
       </c>
       <c r="J1012" s="3" t="n">
-        <v>392263.88</v>
+        <v>987646</v>
       </c>
       <c r="K1012" s="2" t="inlineStr">
         <is>
@@ -52755,27 +52755,27 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
         <is>
-          <t>CLINICA CHUTRO S R L</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D1013" s="2" t="inlineStr">
         <is>
-          <t>30545996991</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E1013" s="2" t="inlineStr">
         <is>
-          <t>00004-00006086</t>
+          <t>00024-00023178</t>
         </is>
       </c>
       <c r="F1013" s="2" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
       <c r="G1013" s="2" t="n">
@@ -52792,11 +52792,11 @@
         </is>
       </c>
       <c r="J1013" s="3" t="n">
-        <v>160910.1</v>
+        <v>276888.6</v>
       </c>
       <c r="K1013" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52808,22 +52808,22 @@
       </c>
       <c r="B1014" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr">
         <is>
-          <t>30566661663</t>
+          <t>30545894528</t>
         </is>
       </c>
       <c r="E1014" s="2" t="inlineStr">
         <is>
-          <t>00005-00007128</t>
+          <t>00024-00023176</t>
         </is>
       </c>
       <c r="F1014" s="2" t="inlineStr">
@@ -52832,7 +52832,7 @@
         </is>
       </c>
       <c r="G1014" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H1014" s="2" t="inlineStr">
         <is>
@@ -52845,11 +52845,11 @@
         </is>
       </c>
       <c r="J1014" s="3" t="n">
-        <v>0</v>
+        <v>187926.14</v>
       </c>
       <c r="K1014" s="2" t="inlineStr">
         <is>
-          <t>calculada</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52859,25 +52859,29 @@
           <t>04-2026</t>
         </is>
       </c>
-      <c r="B1015" s="2" t="inlineStr"/>
+      <c r="B1015" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="C1015" s="2" t="inlineStr">
         <is>
-          <t>INSTITUTO PRIVADO DE NEONATOLOGIA Y PEDIATRIA S.A.</t>
+          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
         </is>
       </c>
       <c r="D1015" s="2" t="inlineStr">
         <is>
-          <t>30659560093</t>
+          <t>30566278207</t>
         </is>
       </c>
       <c r="E1015" s="2" t="inlineStr">
         <is>
-          <t>00500-00044031</t>
+          <t>00060-00000627</t>
         </is>
       </c>
       <c r="F1015" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPM</t>
         </is>
       </c>
       <c r="G1015" s="2" t="n">
@@ -52894,11 +52898,11 @@
         </is>
       </c>
       <c r="J1015" s="3" t="n">
-        <v>1292379.75</v>
+        <v>34045.3</v>
       </c>
       <c r="K1015" s="2" t="inlineStr">
         <is>
-          <t>sin fecha</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
@@ -52908,25 +52912,29 @@
           <t>04-2026</t>
         </is>
       </c>
-      <c r="B1016" s="2" t="inlineStr"/>
+      <c r="B1016" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>INSTITUTO PRIVADO DE NEONATOLOGIA Y PEDIATRIA S.A.</t>
+          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr">
         <is>
-          <t>30659560093</t>
+          <t>30566661663</t>
         </is>
       </c>
       <c r="E1016" s="2" t="inlineStr">
         <is>
-          <t>00500-00044035</t>
+          <t>00005-00007128</t>
         </is>
       </c>
       <c r="F1016" s="2" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
       <c r="G1016" s="2" t="n">
@@ -52943,11 +52951,11 @@
         </is>
       </c>
       <c r="J1016" s="3" t="n">
-        <v>1287167.43</v>
+        <v>0</v>
       </c>
       <c r="K1016" s="2" t="inlineStr">
         <is>
-          <t>sin fecha</t>
+          <t>sugerida</t>
         </is>
       </c>
     </row>
